--- a/data/interactions.xlsx
+++ b/data/interactions.xlsx
@@ -467,12 +467,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ae5119c6-e40a-4c63-822e-edc9f5bcab17</t>
+          <t>e0111762-ca92-4a1e-8fb0-3bea8ef2e263</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>68da5cfc-5a5c-4f30-adec-3b2cf0ad3570</t>
+          <t>95fb50f9-8e76-43b2-978b-80d9a6d705f3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -482,7 +482,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -491,18 +491,18 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46235.51582175926</v>
+        <v>46260.02369212963</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>594ed2ee-bf7e-4d82-9120-b87cf144ec34</t>
+          <t>5b531e11-8d6a-4aa9-ab1d-ff8d4c0fa377</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>f4966cff-6ee5-4e47-8129-b28989be45ec</t>
+          <t>39916282-53f8-424b-b275-93b0af32083d</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -521,18 +521,18 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>46235.51725694445</v>
+        <v>46260.02512731482</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1b49c5fd-419c-4a54-a7e9-7d290cbe280a</t>
+          <t>a439f958-cfbc-4b49-b852-4eb9cf4a1eef</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7848690a-f055-4234-80f1-e4b2ea7be344</t>
+          <t>2af4e67f-a2ba-4237-8675-8f5c38b5056a</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -542,7 +542,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -551,23 +551,23 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46235.51631944445</v>
+        <v>46260.02418981482</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>a05bf230-1a86-4c3b-b76f-3e605084c13c</t>
+          <t>6cb06ad7-0b32-428d-882b-ddaa0fe3663f</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>a2751a9b-6534-403a-ac88-88fd673b80e2</t>
+          <t>4d5b12de-3570-43f7-be5a-5fc9557660f5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -581,18 +581,18 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46235.51631944445</v>
+        <v>46260.02418981482</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>02003f75-d86b-4133-8c4f-d40464bb6f0d</t>
+          <t>e00b3159-0045-43fe-b317-43b509f18cb5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>82fed8e5-31da-4832-a85b-fcc0b091695f</t>
+          <t>59745190-f939-4fbf-b47f-779560330b91</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46235.51697916666</v>
+        <v>46260.02484953704</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5961be05-0c86-4f5b-a7e3-b97e9baf8f8b</t>
+          <t>78c64aa6-8b94-4598-84f6-120df20ffcc8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>d90a4dfc-04c4-4043-908e-a373a8b623ef</t>
+          <t>e578b598-c3e2-4437-a16a-8330b2460873</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -641,18 +641,18 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>46235.51663194445</v>
+        <v>46260.02450231482</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>235609e3-ff61-4c54-b1cc-e89d3a0194a9</t>
+          <t>d49618d0-7ea6-4e67-9f25-fe6f44234fc9</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4753c09d-58f1-4c9c-a01b-32798a8a7e9d</t>
+          <t>42c21d36-88f7-4dd6-be02-20b2eb90c142</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -671,18 +671,18 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46235.51736111111</v>
+        <v>46260.02523148148</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>47ac2d54-8e83-494b-9591-2ffd67277b8a</t>
+          <t>52e78b34-2f45-4b29-9127-ea8cbde19cec</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>34433c4b-31e2-48b8-bf86-5bfad18da944</t>
+          <t>89038be4-842f-4eac-a540-049bf46193e0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -701,23 +701,23 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46235.5171412037</v>
+        <v>46260.02501157407</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>93819f38-5a4a-4c3c-b2fb-67b3664b1f1e</t>
+          <t>8950fb77-8313-4977-9ae8-00671bcbc8f6</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>072fd290-6796-4c10-b607-70db53cdb727</t>
+          <t>50d1690d-e2da-494f-9de5-7b3ffbc71e01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -731,18 +731,18 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>46235.51591435185</v>
+        <v>46260.02378472222</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>c0fa5526-9b8b-43c8-b8ce-635de906ebaf</t>
+          <t>713af190-b6e2-40d8-84b4-2ff25ab2993f</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>cc0a14cf-7493-44f8-a069-694538c421aa</t>
+          <t>972f3eca-17b8-4a72-bcf2-34168a923e4d</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -761,18 +761,18 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>46235.51701388889</v>
+        <v>46260.02488425926</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>29c754b5-8602-43bf-b413-14e1576f30b9</t>
+          <t>d30228bd-7193-40ab-ba1e-471a09d74099</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>9ec9f95e-1468-4c4f-a006-fca793e34aa1</t>
+          <t>21b16158-73f4-451f-b278-396731d71ddf</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -791,18 +791,18 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>46235.51631944445</v>
+        <v>46260.02418981482</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>a4721fde-003d-4161-8be5-fea43c157af2</t>
+          <t>26ed1458-7332-4935-b648-dcbe94f506dc</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7622805e-1891-43b3-9d99-dfe5f0b1ab76</t>
+          <t>70ea0327-6bfa-447e-9874-93aaa1b2f4d2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -821,23 +821,23 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>46235.51600694445</v>
+        <v>46260.02387731482</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3175e04c-0d70-483e-9eda-f459435b0e65</t>
+          <t>f8653372-e220-4d4c-a713-c51795e8d088</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>fad897d1-7f43-45fa-944a-77e9b4494df6</t>
+          <t>4d5b12de-3570-43f7-be5a-5fc9557660f5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -851,23 +851,23 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>46235.5162037037</v>
+        <v>46260.02407407408</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04657f62-25c8-4cef-906f-b0be61a2de23</t>
+          <t>79a134ac-35aa-4b6f-a084-d34930e12db2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>dffd8ecf-ca39-4aa8-b63f-5e476be76235</t>
+          <t>48781524-dc37-4660-adff-9d43533ef266</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -881,28 +881,28 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>46235.51650462963</v>
+        <v>46260.024375</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>579cba26-ee32-41c3-b0f5-1b1805540390</t>
+          <t>260c4acb-fe44-45ea-ad73-b7d54c820981</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2bf49978-fa72-4ec1-ab6d-ce3d0b4ac230</t>
+          <t>f53d985f-2219-497c-93c4-97f25f762f7d</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -911,18 +911,18 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>46235.51596064815</v>
+        <v>46260.02383101852</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>491b2f76-bc7e-47c1-b818-b7a14ee1087d</t>
+          <t>ae45a3dc-7af6-4163-86b7-0c0c245474d3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>c51dd9c0-f03a-4383-b846-cb163e9cb4ba</t>
+          <t>03959483-600c-4879-942b-25902022410d</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -941,18 +941,18 @@
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>46235.51711805556</v>
+        <v>46260.02498842592</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>c5a7f7a2-43fc-4b43-bd70-7c7258e7fdb1</t>
+          <t>76e3a7fc-46c6-47a8-8b27-72bd7909a290</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>fad897d1-7f43-45fa-944a-77e9b4494df6</t>
+          <t>fa6db45d-639a-4ebc-bff1-f5971e108081</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -971,28 +971,28 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>46235.51618055555</v>
+        <v>46260.02405092592</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cc1be69b-5f7c-4e34-9c9e-7914b9cdc4ef</t>
+          <t>4c562cd8-9858-4f0c-9170-9e95cf188329</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0896016c-6271-4a6c-b588-1c2784729302</t>
+          <t>b8df2387-f7f3-44d1-a9d1-290aaeaac9da</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1001,28 +1001,28 @@
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>46235.51728009259</v>
+        <v>46260.02515046296</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9c45165e-c256-4362-a434-697cbd0843ec</t>
+          <t>52ed3360-e004-4a62-af42-7bda874f5177</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>c8ba352f-ba91-4913-975f-71f16968349b</t>
+          <t>2e75c787-cba9-4229-baaf-ccaf703dbe6f</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1031,28 +1031,28 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>46235.51575231482</v>
+        <v>46260.02362268518</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ad0c8b00-b112-440b-87e8-6f27a2022a15</t>
+          <t>02402019-142e-40e2-952b-72828d1be0f3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>831d7f10-2c81-480d-bdae-c7135346307a</t>
+          <t>0fb3c163-9a14-4df4-8457-8cbd3dc5db3f</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1061,28 +1061,28 @@
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>46235.51638888889</v>
+        <v>46260.02425925926</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0ce13b67-92d7-4a70-be5b-4d04e4ac328d</t>
+          <t>b4d5b47f-0fdc-46d3-bb99-0b07d1dd6aa2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>e04548aa-0711-4efa-ab9a-b550021155f7</t>
+          <t>42bbf194-0cb7-44aa-bbae-09280e0d27c8</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1091,18 +1091,18 @@
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>46235.51579861111</v>
+        <v>46260.02366898148</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3a7a1cd5-48f8-43d9-a8d6-e5626b27d556</t>
+          <t>2ffb7029-8ab5-4209-988f-9dfe92a7b064</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7d67b649-2b07-4661-9637-aa9890bf95dc</t>
+          <t>478c6a38-b89d-4bf2-b1c3-a0dcde41a6d6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1121,28 +1121,28 @@
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>46235.51574074074</v>
+        <v>46260.02361111111</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>a5adbe64-b11b-4a23-9424-7d2965ff8de0</t>
+          <t>b6fadf2a-c01b-4b2a-af3b-e6412d000349</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>621ebdc9-8dcf-4dd9-af11-9063b41589dc</t>
+          <t>2af4e67f-a2ba-4237-8675-8f5c38b5056a</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1151,23 +1151,23 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>46235.51598379629</v>
+        <v>46260.02385416667</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>b07c9b54-8354-4f92-a363-1ec5fdd3d231</t>
+          <t>4d9d2239-5f99-461e-bb29-130fc0844d79</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>517f640d-86a9-424b-a565-c57460d72399</t>
+          <t>cc734625-0fd5-4c45-9e15-119fe2d63e41</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1181,28 +1181,28 @@
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>46235.51677083333</v>
+        <v>46260.0246412037</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>57dd58c0-9855-4100-8387-5c9a9ec140e8</t>
+          <t>ac2b0884-82f4-4b5c-a6a0-85812c17c0b2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4b177a79-1e3b-4908-a573-43c662c3a15b</t>
+          <t>89038be4-842f-4eac-a540-049bf46193e0</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1211,18 +1211,18 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>46235.5165162037</v>
+        <v>46260.02438657408</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>c0b5e8f0-9aa3-4a6d-a62f-a7fd17d324d7</t>
+          <t>d373714c-f4c9-46c0-8b6d-a5c937495227</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>fdee9ea9-433b-4446-b620-9be1d2418d97</t>
+          <t>f0be3bff-1962-4c2b-a8bf-931211f4477b</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1241,23 +1241,23 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>46235.51755787037</v>
+        <v>46260.02542824074</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>c82fda54-e3df-4cf2-ab66-3cd93bb433e9</t>
+          <t>87b7ef5c-656e-477a-b84b-4f3a520dcb79</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1779b6fe-21b9-49f3-a23b-0b838095bc4a</t>
+          <t>2913e0e0-acee-4aaa-9356-eeefbcedc009</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1271,23 +1271,23 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>46235.51734953704</v>
+        <v>46260.02521990741</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>f30d907d-03ad-4312-8e71-f5b70d62bba8</t>
+          <t>4d50e042-8e06-475f-83fa-07725c1c223c</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12d56881-85bc-4be4-9a05-a4dc39b3310d</t>
+          <t>f46b2462-0c66-4d81-a4ff-b279f7b44796</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1301,18 +1301,18 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>46235.5177662037</v>
+        <v>46260.02563657407</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>f67eeb51-9099-4361-b6f6-a7a4024c6f4e</t>
+          <t>9632f254-3d64-435b-b2ec-1995bbc98dd3</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>fd223f5c-963b-480c-8c42-2842ebda4d37</t>
+          <t>f0be3bff-1962-4c2b-a8bf-931211f4477b</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1331,28 +1331,28 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>46235.51678240741</v>
+        <v>46260.02465277778</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9a8f7543-2a6f-4ed7-b8b4-264361d27b72</t>
+          <t>cd4d2058-80c3-4738-9455-5f327660e57a</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>d3529462-3595-46e5-8c31-5302aa767759</t>
+          <t>d15737ff-69fb-473d-ba5b-c730bf5cac2a</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1361,18 +1361,18 @@
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>46235.51685185185</v>
+        <v>46260.02472222222</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>b58baf2c-2158-4e3a-b5e4-e35ca5c1b2a1</t>
+          <t>e90425e3-2ec6-4c59-8342-6fc0154a7c0e</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6a63e8be-946a-48d1-bba1-d2b767bbc3e4</t>
+          <t>2daaf217-8834-41f2-8c67-19d093ea7c0c</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1391,18 +1391,18 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>46235.51590277778</v>
+        <v>46260.02377314815</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>7287766f-9eda-465e-9238-c904cba88f4e</t>
+          <t>68272d1e-b6ea-4752-872b-2e838a71ea54</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8892a89b-9ad4-4f12-9eea-7486c41091bc</t>
+          <t>0c1b1e0d-a4f3-4a86-8faa-c5276d9cab1e</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1421,28 +1421,28 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>46235.51739583333</v>
+        <v>46260.0252662037</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>e586d866-f753-4ca2-885c-508c3adda3b6</t>
+          <t>b54de768-85ca-4f42-a781-d0dc2f4e419d</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>edf33408-32f0-4023-8f23-d2976b8c6f24</t>
+          <t>d15737ff-69fb-473d-ba5b-c730bf5cac2a</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1451,28 +1451,28 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>46235.5159375</v>
+        <v>46260.02380787037</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>e731cadf-88e2-44e0-8b43-605625410e5f</t>
+          <t>b27b7642-7747-455f-9c12-17f6fa576c56</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1051c4e6-abaf-4d9c-a518-d7ffebbe4f4c</t>
+          <t>2febe67b-0ff0-4a57-8df5-6dff3dceebfa</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1481,18 +1481,18 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>46235.51659722222</v>
+        <v>46260.02446759259</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>245e7ebc-073a-40cd-ac13-acc5f92b3350</t>
+          <t>0ca95b18-9131-4576-b618-6caa3d3e96ae</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>4753c09d-58f1-4c9c-a01b-32798a8a7e9d</t>
+          <t>178dc3a5-ac00-4268-8cd4-9d9bab93c92a</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1511,18 +1511,18 @@
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>46235.51725694445</v>
+        <v>46260.02512731482</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>7be86b6a-5e7c-4de7-8665-668dd5461fa1</t>
+          <t>3810609d-3e87-43c5-abda-035d5e9527f4</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>aa967b86-29e7-44cb-8c51-f657d380b15b</t>
+          <t>483718f8-e416-41cd-904d-7a237019c393</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1541,28 +1541,28 @@
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>46235.51696759259</v>
+        <v>46260.02483796296</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5fc5c10e-4064-4207-acdf-a5e7446eb487</t>
+          <t>ac1b4da9-cade-4a37-8a8e-316080768628</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>d40f84a3-dffa-46b0-bfff-af7f48f052ea</t>
+          <t>28dbf010-d41e-4831-bb00-52d51749884b</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1571,28 +1571,28 @@
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>46235.51674768519</v>
+        <v>46260.02461805556</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2de1d17c-fee3-47ba-ad13-a624fcefac23</t>
+          <t>5df2de3e-0828-4eb2-95ea-1f6387d209e2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>c6842666-a65a-4f9c-acd6-ea0c94e8b0e4</t>
+          <t>a85a9f03-5ea4-4700-a65b-a79f0fac294f</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1601,28 +1601,28 @@
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>46235.51732638889</v>
+        <v>46260.02519675926</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>41374194-f923-4570-9958-261ed2847ae9</t>
+          <t>afe2838d-caff-47c8-9cb9-a1e11b22eed8</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>fc155d42-7dc6-4b47-8804-bc542c1c697c</t>
+          <t>74dcaab0-ca92-4995-a856-2eec8c712296</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1631,18 +1631,18 @@
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>46235.51571759259</v>
+        <v>46260.02358796296</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6c4a58a8-c8be-481e-9f40-e08e83a8c6c7</t>
+          <t>27419f98-0db8-4582-8076-4ade31a6b0ba</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>528e0b43-675f-4a03-bf5f-78a08c2a4203</t>
+          <t>2daaf217-8834-41f2-8c67-19d093ea7c0c</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1661,28 +1661,28 @@
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>46235.51739583333</v>
+        <v>46260.0252662037</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ef115d08-e858-450f-b07a-6b0319f785be</t>
+          <t>6aae08c0-c82a-4311-ae25-25c3367bcbe8</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>217d8d97-267f-42b8-b0c4-0e9892150141</t>
+          <t>f2029fb7-2b7a-4d0f-8151-0bb51d7d1a1e</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1691,23 +1691,23 @@
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>46235.51658564815</v>
+        <v>46260.02445601852</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>80d9eaf8-2753-4d6f-9978-44d2a861f29a</t>
+          <t>8b422146-49eb-4461-94f6-204f3c4873d7</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ca0e932a-fd81-474f-98cc-1fbc739211f1</t>
+          <t>87eefbeb-8468-47a5-a5ef-8076259e3d8c</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1721,28 +1721,28 @@
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>46235.51774305556</v>
+        <v>46260.02561342593</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4e6d259c-2d64-4cdc-b970-60f9f3f8b2ec</t>
+          <t>01701970-d3c7-4dd0-82b3-cf1ed2ed83a8</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>e6da211a-5cf8-4a9f-894d-c96c91a0d094</t>
+          <t>2ea2e1c1-fe6c-4ea1-b686-e385ea34fce0</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1751,18 +1751,18 @@
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>46235.51637731482</v>
+        <v>46260.02424768519</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>72c37e71-98cf-4dfd-a29b-f082cae90d11</t>
+          <t>778d8522-3c25-43e6-b95e-4bda83e47372</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>c8ba352f-ba91-4913-975f-71f16968349b</t>
+          <t>6e932cf0-f369-4379-8e7e-1913eb40bf4a</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1781,18 +1781,18 @@
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>46235.51746527778</v>
+        <v>46260.02533564815</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>696a6e11-1298-49f1-b175-6d253dd56981</t>
+          <t>22ee3c0f-0bb4-46e2-b167-59703126354f</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>73b70ed3-a36d-4983-a36a-8b78e2358d5d</t>
+          <t>fa6db45d-639a-4ebc-bff1-f5971e108081</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1811,23 +1811,23 @@
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>46235.51609953704</v>
+        <v>46260.02396990741</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>955ac4e1-b4ee-4e69-894b-5f6750ef4c01</t>
+          <t>05b9badb-f0c4-4f43-862f-e1836a0f103c</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>528e0b43-675f-4a03-bf5f-78a08c2a4203</t>
+          <t>478c6a38-b89d-4bf2-b1c3-a0dcde41a6d6</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1841,28 +1841,28 @@
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>46235.51768518519</v>
+        <v>46260.02555555556</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2bd45250-32b6-414b-a487-f712f89fbc02</t>
+          <t>e29f734c-ba6e-4835-8351-8094cd205a41</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>14c667e1-3449-4271-b46c-b306d6a8c9d6</t>
+          <t>85c7853f-a416-49fb-a6e1-5b5056b7096f</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1871,18 +1871,18 @@
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>46235.51583333333</v>
+        <v>46260.0237037037</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>a525a99b-d6e3-43bd-a371-d484ad47cfb7</t>
+          <t>1de5b408-31f9-4b42-abf7-4afb184eb149</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>73b70ed3-a36d-4983-a36a-8b78e2358d5d</t>
+          <t>776377e7-b6f2-4c6f-89bf-4a89a9270e83</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1901,18 +1901,18 @@
         </is>
       </c>
       <c r="F49" s="2" t="n">
-        <v>46235.51655092592</v>
+        <v>46260.02442129629</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>b26718e6-43df-4430-b8e9-91e56552f7e7</t>
+          <t>8aa259ca-4b2b-4b50-9ea2-cb713c207239</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>232a8a87-2155-40f0-bd81-263575258afe</t>
+          <t>aa51e5f0-271f-47b7-af78-18b296e37c38</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1931,18 +1931,18 @@
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>46235.51633101852</v>
+        <v>46260.02420138889</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1403c15a-810b-4562-96a0-9b04659a8f8c</t>
+          <t>f82447fb-2f64-4f05-a8dd-02d6fd967b9d</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>f125b3f0-7ee8-411f-9efc-6527c7e1b06e</t>
+          <t>e1703452-4f07-41fe-809c-f9f7e63f536b</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1961,18 +1961,18 @@
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>46235.51766203704</v>
+        <v>46260.02553240741</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>02fe7db3-7486-4370-a6a7-15d7112a9004</t>
+          <t>7fe0c1dc-bedb-46f1-a17c-028a83d16a48</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>c8ba352f-ba91-4913-975f-71f16968349b</t>
+          <t>b3bbe817-7db0-4cf1-b86b-37bd65943248</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1991,18 +1991,18 @@
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>46235.51601851852</v>
+        <v>46260.02388888889</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>526d0e8e-23c9-4648-885a-82d179d91db0</t>
+          <t>071ffaac-84c5-4deb-ac5e-992bd4b2b552</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>7ef9145d-263a-4a30-8fcc-bf33769fcada</t>
+          <t>575ebed8-a5ac-49dc-b418-6417a95748a0</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2021,18 +2021,18 @@
         </is>
       </c>
       <c r="F53" s="2" t="n">
-        <v>46235.51663194445</v>
+        <v>46260.02450231482</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>a52f0948-2f1d-4e92-91d3-0b3fa5ede27f</t>
+          <t>44deef30-cbd4-4a68-89d5-db224c50d08e</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>f400192e-4d6f-4f9f-8b33-bcf900ded667</t>
+          <t>ec27f6a3-118a-4d53-b512-415e59ff7e23</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2051,18 +2051,18 @@
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>46235.51672453704</v>
+        <v>46260.02459490741</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4f7bc46c-aace-4bd5-ac4a-283e84a727a5</t>
+          <t>aad3665b-f854-4494-9f67-602ecb274735</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ab5b6657-5809-4215-bf7f-61b2a238ee47</t>
+          <t>fb408916-cd92-43cf-b606-fde8cecf8d71</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2081,23 +2081,23 @@
         </is>
       </c>
       <c r="F55" s="2" t="n">
-        <v>46235.51734953704</v>
+        <v>46260.02521990741</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>d10a2c04-936c-45ce-bfa7-9941ab8bbf8f</t>
+          <t>6f4999d9-0a18-42cc-96c4-3431a5da1bc9</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>c65c78c9-446b-4ee3-9a13-bd00c60f89d9</t>
+          <t>67e56e91-8a9d-404b-b870-8db751571e05</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2111,18 +2111,18 @@
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>46235.51693287037</v>
+        <v>46260.02480324074</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>e7304197-8e06-433b-985b-2486d510ad41</t>
+          <t>ac239a55-9b2f-406a-8dc5-846a7792ef8c</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>e9ae134d-dca7-4a7c-91a2-bcba010616bf</t>
+          <t>50d4198a-a465-484b-bb3f-467c0dc71f5e</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2141,28 +2141,28 @@
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>46235.51629629629</v>
+        <v>46260.02416666667</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>e1a93b38-ff57-40b6-a5d9-a86dd51c434d</t>
+          <t>ebeb4b63-cdcf-474c-a919-e2e2d8349db4</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>e04548aa-0711-4efa-ab9a-b550021155f7</t>
+          <t>d8832129-bed7-41dd-8635-4db7bdc3afb1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2171,18 +2171,18 @@
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>46235.51737268519</v>
+        <v>46260.02524305556</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>153ce64d-1b05-4659-a6f7-a2d58d585826</t>
+          <t>5725e0e3-fedc-4e46-9250-8a7a0a292153</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>d469e12d-956a-4e2a-89e1-75db9f7448cb</t>
+          <t>c8e35c42-6053-4113-a599-7cc79283d867</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2201,28 +2201,28 @@
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>46235.51692129629</v>
+        <v>46260.02479166666</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>666ed017-225d-4d9e-888f-4078c652cfc4</t>
+          <t>273fe2c5-4ff3-4a73-9a04-b46813494049</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0c29877d-9f9e-434b-9220-a4d06f94a13d</t>
+          <t>6f586dd0-d848-4db7-8431-723fe6e5dd48</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2231,18 +2231,18 @@
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>46235.5175</v>
+        <v>46260.02537037037</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>19ed8d30-69c5-42c6-943d-448566e86311</t>
+          <t>1c926be0-f4f7-4e19-84fd-4c26de9a70a1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>3acf9e38-628c-402e-9fa3-27c0b34dd9a5</t>
+          <t>80001165-bfd4-436f-a450-21d6ea84544d</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2261,28 +2261,28 @@
         </is>
       </c>
       <c r="F61" s="2" t="n">
-        <v>46235.51618055555</v>
+        <v>46260.02405092592</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ab06e3f1-4449-4f7f-bb7d-3105593a68c6</t>
+          <t>b44eebae-df78-4663-a4b0-355542eb2d40</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>bcfafb41-c981-497c-b534-9959fcec4b9b</t>
+          <t>1138590b-c95e-4018-9e77-1d096e3c9cdf</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2291,28 +2291,28 @@
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>46235.51630787037</v>
+        <v>46260.02417824074</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>6a2125d3-a80d-412d-afea-803ecf03e48a</t>
+          <t>c152374f-b76a-4904-8727-d90c6f5ddf0f</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>555e9abe-b3c8-474f-96b5-ca67c51736ad</t>
+          <t>70ea0327-6bfa-447e-9874-93aaa1b2f4d2</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2321,18 +2321,18 @@
         </is>
       </c>
       <c r="F63" s="2" t="n">
-        <v>46235.51643518519</v>
+        <v>46260.02430555555</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>9b090dd1-2af3-4f95-b182-a224bc9a3eb0</t>
+          <t>0c63014a-bb4a-48f8-9b16-b124d1e71a45</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>850b518e-b3f3-4499-90de-e53f12082502</t>
+          <t>03ef7674-d310-4656-89de-08e3f167e1ba</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2351,18 +2351,18 @@
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>46235.51724537037</v>
+        <v>46260.02511574074</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>98c1bcda-7c05-4ca1-9246-26aad0ab2128</t>
+          <t>bfc73b1d-c497-48db-8f82-e1cdefb1937f</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>92c7e79f-a989-4305-ba48-2af36ce8d6d6</t>
+          <t>154a3ed4-2a2d-4ca9-8e50-06aaf6333c6d</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2381,28 +2381,28 @@
         </is>
       </c>
       <c r="F65" s="2" t="n">
-        <v>46235.51734953704</v>
+        <v>46260.02521990741</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>7c424201-4790-4222-87bb-aa3098b35f33</t>
+          <t>0626df93-cc22-4c88-9312-ecd6340d784a</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>73b70ed3-a36d-4983-a36a-8b78e2358d5d</t>
+          <t>9abe646f-9247-4c8f-8c1d-509abe328744</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2411,28 +2411,28 @@
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>46235.51585648148</v>
+        <v>46260.02372685185</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5c88f73b-c70d-405c-b332-41ccfd6b5e2c</t>
+          <t>d6855c53-674b-4ddf-8511-e03881e96b98</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>12d56881-85bc-4be4-9a05-a4dc39b3310d</t>
+          <t>637f52b2-ab9c-41c3-b9d5-12fafc1d3930</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2441,18 +2441,18 @@
         </is>
       </c>
       <c r="F67" s="2" t="n">
-        <v>46235.51704861111</v>
+        <v>46260.02491898148</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>6f49a878-abb0-4782-a0a0-afc55dd141fc</t>
+          <t>95b09883-c496-42a4-8eb1-050b9fd23744</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>232a8a87-2155-40f0-bd81-263575258afe</t>
+          <t>b3bbe817-7db0-4cf1-b86b-37bd65943248</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2471,18 +2471,18 @@
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>46235.51684027778</v>
+        <v>46260.02471064815</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>e0592fc0-b7cd-41ad-b99d-3665276da811</t>
+          <t>e0f9554f-c597-447e-9a01-98ef937448da</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>c2450c37-1faf-4512-8157-b4fde08652c4</t>
+          <t>9432ebb6-935a-449b-b05d-c19defa24cbb</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2501,18 +2501,18 @@
         </is>
       </c>
       <c r="F69" s="2" t="n">
-        <v>46235.51660879629</v>
+        <v>46260.02447916667</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>293c77b5-6716-4bec-8f5a-9c8e59011b9a</t>
+          <t>cc93d203-e28b-4a47-9c89-2076919a5b37</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>f4845210-5c2a-4fc4-8afe-cdecde3fc266</t>
+          <t>0566f9df-30ab-44ee-81c2-56f47a689fbc</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2531,18 +2531,18 @@
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>46235.51717592592</v>
+        <v>46260.02504629629</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>24bf339f-3c52-44fc-aceb-91aa4caa18c0</t>
+          <t>2d238c09-f102-4dad-aca5-b128ebbb9b03</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>6a63e8be-946a-48d1-bba1-d2b767bbc3e4</t>
+          <t>d8832129-bed7-41dd-8635-4db7bdc3afb1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2561,18 +2561,18 @@
         </is>
       </c>
       <c r="F71" s="2" t="n">
-        <v>46235.51734953704</v>
+        <v>46260.02521990741</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>bf0f0c7e-26b1-407c-b6c5-6ce449933155</t>
+          <t>804a8efd-5b20-4a69-aaf3-82869438ce2c</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>7853563e-dd48-4b33-bee8-b176567a1ff7</t>
+          <t>03959483-600c-4879-942b-25902022410d</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2591,23 +2591,23 @@
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>46235.51596064815</v>
+        <v>46260.02383101852</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>c4d204db-1977-4828-9a30-f79620351595</t>
+          <t>87522b79-f450-4668-9b5f-ab4075bb4bb5</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>f5682ea1-5450-43ea-84c9-4daeb84ee1f9</t>
+          <t>87eefbeb-8468-47a5-a5ef-8076259e3d8c</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2621,28 +2621,28 @@
         </is>
       </c>
       <c r="F73" s="2" t="n">
-        <v>46235.51739583333</v>
+        <v>46260.0252662037</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>65f75778-a1bd-4e51-b90f-ec90090ddb96</t>
+          <t>f95f7556-7f3c-46d7-aca9-7cc06f9706d6</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>34a65bc4-fc94-4270-ab14-0d8e912aa2ba</t>
+          <t>2febe67b-0ff0-4a57-8df5-6dff3dceebfa</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2651,18 +2651,18 @@
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>46235.51775462963</v>
+        <v>46260.025625</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>8d832ccb-8f56-4d51-9ea2-a39066c98035</t>
+          <t>77f5b49d-0911-4937-bf60-a7db9a829e43</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>e3354617-c494-4f88-bef9-1e02a7d7f925</t>
+          <t>fb408916-cd92-43cf-b606-fde8cecf8d71</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2681,23 +2681,23 @@
         </is>
       </c>
       <c r="F75" s="2" t="n">
-        <v>46235.51774305556</v>
+        <v>46260.02561342593</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>31f7445e-582a-43de-bf16-b7c88fd50263</t>
+          <t>df3c5c5e-8cfe-4fa0-bf6a-af86fc9d3b20</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>6b90194a-ebb3-4865-95e0-b3eb31a8eac8</t>
+          <t>87eefbeb-8468-47a5-a5ef-8076259e3d8c</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2711,28 +2711,28 @@
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>46235.51623842592</v>
+        <v>46260.02410879629</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>db16612a-1397-4605-93a0-6f3b728784aa</t>
+          <t>4d4ed520-0ca3-41cb-8bce-b85448bcf7a0</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>8b907a52-4244-4158-8411-fd60712cebf5</t>
+          <t>f2029fb7-2b7a-4d0f-8151-0bb51d7d1a1e</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2741,18 +2741,18 @@
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>46235.51633101852</v>
+        <v>46260.02420138889</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>6b8b41d8-850c-4680-8837-baf91a40ee79</t>
+          <t>82e47f57-7625-4663-b02b-4df5f1e4bd21</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>308ebee4-cf75-4efb-86cb-6aa765769eee</t>
+          <t>6dc21962-76e3-4c06-be70-10b076d513f7</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2771,28 +2771,28 @@
         </is>
       </c>
       <c r="F78" s="2" t="n">
-        <v>46235.51571759259</v>
+        <v>46260.02358796296</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>df3648d3-3d1c-4b50-ae15-c6c4015d9ae2</t>
+          <t>341d3744-297f-4934-ad36-8e8c5e5244ee</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>e04548aa-0711-4efa-ab9a-b550021155f7</t>
+          <t>8f68b6e4-631e-41dc-a203-c75611ebbdde</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2801,18 +2801,18 @@
         </is>
       </c>
       <c r="F79" s="2" t="n">
-        <v>46235.51670138889</v>
+        <v>46260.02457175926</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4ae4969d-2b1a-4126-92f7-1dd8abbc41cd</t>
+          <t>7b637600-242d-4ccc-af36-53a88d95a7b9</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>c2450c37-1faf-4512-8157-b4fde08652c4</t>
+          <t>8f68b6e4-631e-41dc-a203-c75611ebbdde</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2831,18 +2831,18 @@
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>46235.51658564815</v>
+        <v>46260.02445601852</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>86ae9e86-a35d-4c5d-a14c-925bfe9b2e72</t>
+          <t>cbbb4b29-9f92-41a4-9355-b9857ef29fb7</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>4b177a79-1e3b-4908-a573-43c662c3a15b</t>
+          <t>aa4952cc-be1c-43ef-8fbe-0a28811e57bc</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2861,18 +2861,18 @@
         </is>
       </c>
       <c r="F81" s="2" t="n">
-        <v>46235.51619212963</v>
+        <v>46260.0240625</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5aaf5201-e41a-40a7-bc62-94ad5657aa72</t>
+          <t>a844b312-0f48-4e1f-b989-77d43d4c360e</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>c2450c37-1faf-4512-8157-b4fde08652c4</t>
+          <t>24aed73a-55a4-4ad2-961a-fa5d278c3bc3</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2891,28 +2891,28 @@
         </is>
       </c>
       <c r="F82" s="2" t="n">
-        <v>46235.51725694445</v>
+        <v>46260.02512731482</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0cbc8180-6902-4210-91c6-e016b81dee03</t>
+          <t>67a86449-198f-4716-9d3c-7c4fbd379fdf</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>b4bcd554-429d-4560-9171-eecf27d4d4b4</t>
+          <t>70ea0327-6bfa-447e-9874-93aaa1b2f4d2</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2921,18 +2921,18 @@
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>46235.51671296296</v>
+        <v>46260.02458333333</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>7a6cc708-c45e-4c20-a9f2-655c164e6417</t>
+          <t>624a8eaf-a79a-4395-bcac-7b0ffb2504b6</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>3fb7fd85-868b-44a1-9a49-cc8a0c6772b1</t>
+          <t>50d1690d-e2da-494f-9de5-7b3ffbc71e01</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2951,18 +2951,18 @@
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>46235.51724537037</v>
+        <v>46260.02511574074</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>c6c1665b-2bcc-41ab-acb4-74a8e390442c</t>
+          <t>b93f0cf9-31c2-475b-8f86-851a9e9042bb</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1051c4e6-abaf-4d9c-a518-d7ffebbe4f4c</t>
+          <t>0c1b1e0d-a4f3-4a86-8faa-c5276d9cab1e</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2981,28 +2981,28 @@
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>46235.51724537037</v>
+        <v>46260.02511574074</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>04f59bb2-0525-417f-9ea6-8e6aef46d8a0</t>
+          <t>14135426-f381-4a80-afc3-fff99d3adaa4</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>8a3b6556-dee6-4dd2-8499-59932b7a2b84</t>
+          <t>cc734625-0fd5-4c45-9e15-119fe2d63e41</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3011,18 +3011,18 @@
         </is>
       </c>
       <c r="F86" s="2" t="n">
-        <v>46235.51650462963</v>
+        <v>46260.024375</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>77710db1-c67b-4687-8990-6a62ac8cc3e8</t>
+          <t>35e0413b-0d62-4664-b1be-1ff54a13586b</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>f6836f72-41ca-46a4-a558-d77e1f0eebf0</t>
+          <t>ce6c30f4-ac3a-4b5c-81d0-f7f9c1d356d6</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3041,18 +3041,18 @@
         </is>
       </c>
       <c r="F87" s="2" t="n">
-        <v>46235.51650462963</v>
+        <v>46260.024375</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>a102476a-720b-47bd-8dc7-1f4d0ec3e09f</t>
+          <t>3014614b-1e27-4ec5-bfeb-d8f644fbedac</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>8ec5a72f-306a-4db1-9c6e-8bb0901c4600</t>
+          <t>74dcaab0-ca92-4995-a856-2eec8c712296</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3071,18 +3071,18 @@
         </is>
       </c>
       <c r="F88" s="2" t="n">
-        <v>46235.51584490741</v>
+        <v>46260.02371527778</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>59d8ba6b-14b2-4607-ae41-5f1eeadd0d30</t>
+          <t>44af07dd-02b1-4d42-aa93-c6c7f00f527a</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>6a63e8be-946a-48d1-bba1-d2b767bbc3e4</t>
+          <t>984f1c30-52c6-424e-bc11-911875cf29a7</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3101,28 +3101,28 @@
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>46235.5174537037</v>
+        <v>46260.02532407407</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>44606ba4-5e10-41e7-8c06-35a695b5fc06</t>
+          <t>d0620909-f66d-49dd-b870-3c07f0c9ade2</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>f0b2aa71-8809-4d4a-a04f-dfcb3b546765</t>
+          <t>0214df66-56e6-43d6-ba3c-c656cd409072</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3131,18 +3131,18 @@
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>46235.51708333333</v>
+        <v>46260.0249537037</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>723e9c1d-a6ea-497d-9f8a-bd448f6de003</t>
+          <t>1dd531bb-d532-4424-aeaa-fc083fd338d1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>edf33408-32f0-4023-8f23-d2976b8c6f24</t>
+          <t>0c1b1e0d-a4f3-4a86-8faa-c5276d9cab1e</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3161,28 +3161,28 @@
         </is>
       </c>
       <c r="F91" s="2" t="n">
-        <v>46235.51752314815</v>
+        <v>46260.02539351852</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>9536c0f5-9959-4ee1-89ba-9d68a05bf6d8</t>
+          <t>ec8660f3-bd65-47d7-b6de-542fb9f8a594</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>edf33408-32f0-4023-8f23-d2976b8c6f24</t>
+          <t>eb4dfbe2-142c-41d0-97d1-eb96e9c5681f</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3191,18 +3191,18 @@
         </is>
       </c>
       <c r="F92" s="2" t="n">
-        <v>46235.51673611111</v>
+        <v>46260.02460648148</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>7e4ea185-3ee1-4a93-8285-78b97a734e14</t>
+          <t>bce4c931-ef8b-473c-804e-e0904459f8e0</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>7853563e-dd48-4b33-bee8-b176567a1ff7</t>
+          <t>027f5e4d-00c8-4543-847e-dee93a96d0d3</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3221,18 +3221,18 @@
         </is>
       </c>
       <c r="F93" s="2" t="n">
-        <v>46235.51688657407</v>
+        <v>46260.02475694445</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>b716f42f-f3db-4ef9-af58-34bf610411c7</t>
+          <t>eec3d210-cbe8-4748-a46b-b3b535761dca</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>e3354617-c494-4f88-bef9-1e02a7d7f925</t>
+          <t>15b29fb8-7d6d-4b8d-913e-9a965faef996</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3251,28 +3251,28 @@
         </is>
       </c>
       <c r="F94" s="2" t="n">
-        <v>46235.51766203704</v>
+        <v>46260.02553240741</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>516d1dcf-f9a1-4588-8c8a-20266eb44959</t>
+          <t>8a2a31eb-f76d-4a7b-970a-98348016f3aa</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0796c5fe-2105-4e74-b064-f89225821e18</t>
+          <t>6469a201-c598-4bc6-b451-765e0d37845d</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3281,28 +3281,28 @@
         </is>
       </c>
       <c r="F95" s="2" t="n">
-        <v>46235.51598379629</v>
+        <v>46260.02385416667</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>b02b7629-ee5d-4372-a884-dba5c00ed8c1</t>
+          <t>ac9ae5d7-addc-47b3-a05e-33b8dd38cbaa</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>d40f84a3-dffa-46b0-bfff-af7f48f052ea</t>
+          <t>d15737ff-69fb-473d-ba5b-c730bf5cac2a</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3311,28 +3311,28 @@
         </is>
       </c>
       <c r="F96" s="2" t="n">
-        <v>46235.51741898148</v>
+        <v>46260.02528935186</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>b08c330d-3c10-49cd-ad3f-354ca5f3f94b</t>
+          <t>caf53cc7-298a-4fae-b995-ddd6ab4a89a8</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>f4966cff-6ee5-4e47-8129-b28989be45ec</t>
+          <t>396c1e36-a8e3-49df-8111-eddd5ef90cd8</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3341,28 +3341,28 @@
         </is>
       </c>
       <c r="F97" s="2" t="n">
-        <v>46235.51630787037</v>
+        <v>46260.02417824074</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ea96fd05-4a6b-4e3e-a22d-0a0d9b7f00da</t>
+          <t>7c7b8aa6-f9b0-46d6-ad06-6ab610fd9b85</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>8b907a52-4244-4158-8411-fd60712cebf5</t>
+          <t>80001165-bfd4-436f-a450-21d6ea84544d</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3371,18 +3371,18 @@
         </is>
       </c>
       <c r="F98" s="2" t="n">
-        <v>46235.51721064815</v>
+        <v>46260.02508101852</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>9cc53e44-9cef-46ac-aaf3-11527e10576e</t>
+          <t>2e2577fe-8008-440f-8638-900ed228bd58</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>3acf9e38-628c-402e-9fa3-27c0b34dd9a5</t>
+          <t>776377e7-b6f2-4c6f-89bf-4a89a9270e83</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3401,28 +3401,28 @@
         </is>
       </c>
       <c r="F99" s="2" t="n">
-        <v>46235.51697916666</v>
+        <v>46260.02484953704</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>17cd22bf-36ca-4edd-816b-79b584a6ff8e</t>
+          <t>c1c929e8-98b2-42b3-9421-08201315b942</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>a54bb03a-57d6-4643-91a6-5921e8151ec4</t>
+          <t>de51a2d1-45e9-4794-91de-bf6d1cee9fa0</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3431,18 +3431,18 @@
         </is>
       </c>
       <c r="F100" s="2" t="n">
-        <v>46235.51768518519</v>
+        <v>46260.02555555556</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>64d57261-2ba7-4fe2-a35d-1c5ec87f7284</t>
+          <t>83b765bf-d98d-4e9b-a1e3-328a31896a84</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0a4650bd-4472-4b05-a73d-ab41d73c93d9</t>
+          <t>a1278a28-b565-42d8-8711-df11f4bd94a1</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3461,18 +3461,18 @@
         </is>
       </c>
       <c r="F101" s="2" t="n">
-        <v>46235.51594907408</v>
+        <v>46260.02381944445</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>f2581231-f895-44dd-89e9-81493554f9cd</t>
+          <t>ac90bc2b-4e13-417e-8c17-88a99e55b665</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>14c5ceed-1c70-46f9-909f-fb591e389f19</t>
+          <t>328cd713-fb14-4086-99b8-57a7055eff30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3491,18 +3491,18 @@
         </is>
       </c>
       <c r="F102" s="2" t="n">
-        <v>46235.51721064815</v>
+        <v>46260.02508101852</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>af21c06c-53f0-436e-a5ef-45ef7f6711db</t>
+          <t>60dc6d3f-2192-4c1b-870a-e3157cb9691b</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>e04548aa-0711-4efa-ab9a-b550021155f7</t>
+          <t>0fb3c163-9a14-4df4-8457-8cbd3dc5db3f</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3521,28 +3521,28 @@
         </is>
       </c>
       <c r="F103" s="2" t="n">
-        <v>46235.51678240741</v>
+        <v>46260.02465277778</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>9e49cbfe-2e6f-4c23-9f4e-e0cb6c7ef8db</t>
+          <t>98fa4ed3-b3c8-49f4-806d-e29afe56292e</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>e210878d-9aeb-48b8-b43e-0950146d4e39</t>
+          <t>a9e6c2fa-ce6b-47ce-899f-87e62ec565e5</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3551,28 +3551,28 @@
         </is>
       </c>
       <c r="F104" s="2" t="n">
-        <v>46235.51612268519</v>
+        <v>46260.02399305555</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>e5f169d4-98bd-4d80-a7e7-f43bdef04e2c</t>
+          <t>16acdbc8-7355-43bc-9e78-54b7b9b42b0a</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>69b84e67-3b6f-43f6-be94-61afd6b646f9</t>
+          <t>aa51e5f0-271f-47b7-af78-18b296e37c38</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -3581,18 +3581,18 @@
         </is>
       </c>
       <c r="F105" s="2" t="n">
-        <v>46235.51741898148</v>
+        <v>46260.02528935186</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>080ba438-79c1-4a84-96ab-cb0a53cf6d19</t>
+          <t>949538e4-435e-4fe3-bbb1-8731972d70e5</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>424d4004-6fbb-426b-81d2-0216c2bf29fc</t>
+          <t>42c21d36-88f7-4dd6-be02-20b2eb90c142</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3611,23 +3611,23 @@
         </is>
       </c>
       <c r="F106" s="2" t="n">
-        <v>46235.51657407408</v>
+        <v>46260.02444444445</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>50f82bcd-235f-43b5-81cc-74679f3ee97b</t>
+          <t>7914fedc-c691-4cc4-89d1-aaa31bbd4c8c</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>e9ae134d-dca7-4a7c-91a2-bcba010616bf</t>
+          <t>50d1690d-e2da-494f-9de5-7b3ffbc71e01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3641,28 +3641,28 @@
         </is>
       </c>
       <c r="F107" s="2" t="n">
-        <v>46235.51765046296</v>
+        <v>46260.02552083333</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>00b92334-1ad2-4dad-b2e9-0070f845774b</t>
+          <t>d7cec2c9-cb5f-4b8f-9f18-3b08954bb1ea</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>df6d1ab4-9fae-42b8-9b05-3ae9c16e5348</t>
+          <t>0e417481-5ee5-4055-9da6-a4f662e8b91e</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3671,18 +3671,18 @@
         </is>
       </c>
       <c r="F108" s="2" t="n">
-        <v>46235.51645833333</v>
+        <v>46260.0243287037</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>4f43621b-59ee-4498-a417-3bfc7c24f0a1</t>
+          <t>8993fec1-46e5-4268-a6b1-cff96cf0710f</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>c54622a9-766f-4b0a-9ca6-107e30205d18</t>
+          <t>cc734625-0fd5-4c45-9e15-119fe2d63e41</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3701,18 +3701,18 @@
         </is>
       </c>
       <c r="F109" s="2" t="n">
-        <v>46235.51621527778</v>
+        <v>46260.02408564815</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>b2949077-bbaf-4e80-b4a6-e3de98e67574</t>
+          <t>d3f2c6d3-2467-4e1f-8ba9-62f67b633bad</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>f0b2aa71-8809-4d4a-a04f-dfcb3b546765</t>
+          <t>9515ce6e-7689-4e02-8a11-8168a1619836</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3731,18 +3731,18 @@
         </is>
       </c>
       <c r="F110" s="2" t="n">
-        <v>46235.51716435186</v>
+        <v>46260.02503472222</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ec0ffd62-7ab9-4311-bdb0-4fd96c691929</t>
+          <t>1b83e767-6e17-4b4f-bca2-f2107cb8c4b4</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>a422221f-c158-493f-b929-a94c04685538</t>
+          <t>b3bbe817-7db0-4cf1-b86b-37bd65943248</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3761,18 +3761,18 @@
         </is>
       </c>
       <c r="F111" s="2" t="n">
-        <v>46235.51688657407</v>
+        <v>46260.02475694445</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>aaf0a602-29f3-4d96-a0c9-5df220a148a7</t>
+          <t>75660ae6-73fa-4160-9680-7dec66754aa6</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>00ad1ffd-ca29-4f64-8188-f2a50b1e66c0</t>
+          <t>de51a2d1-45e9-4794-91de-bf6d1cee9fa0</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -3791,18 +3791,18 @@
         </is>
       </c>
       <c r="F112" s="2" t="n">
-        <v>46235.51770833333</v>
+        <v>46260.0255787037</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ff271da6-99a6-4ee0-ae47-7559f552d45f</t>
+          <t>770ee376-d7f8-4fda-a5e9-238dbba134e5</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>b0f3a909-ced0-49cd-b8b4-434502df5de6</t>
+          <t>0099e5cc-8754-4617-9a31-0e75f627fb47</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -3821,23 +3821,23 @@
         </is>
       </c>
       <c r="F113" s="2" t="n">
-        <v>46235.51649305555</v>
+        <v>46260.02436342592</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>c5292d63-a10d-4711-8ae8-11997fd6bd6d</t>
+          <t>bf23fd2f-4f13-4e3d-8d7f-572b4b2435a5</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>d3529462-3595-46e5-8c31-5302aa767759</t>
+          <t>10b429ae-1867-484b-9708-7a09429e758c</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3851,18 +3851,18 @@
         </is>
       </c>
       <c r="F114" s="2" t="n">
-        <v>46235.51724537037</v>
+        <v>46260.02511574074</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>5667d1cf-5bb5-455a-94b3-d78d1c45e148</t>
+          <t>4d05ff43-aa01-4351-8a89-6fe0bb08c9ee</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>edf33408-32f0-4023-8f23-d2976b8c6f24</t>
+          <t>15b29fb8-7d6d-4b8d-913e-9a965faef996</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -3881,28 +3881,28 @@
         </is>
       </c>
       <c r="F115" s="2" t="n">
-        <v>46235.51653935185</v>
+        <v>46260.02440972222</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>9bccf053-ec21-4a1e-aeba-1b6f75d9b42f</t>
+          <t>a4262412-9c98-4377-90f2-783e6d0873ed</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1dd255e8-44c5-4366-ab9e-bf381a96ff51</t>
+          <t>de51a2d1-45e9-4794-91de-bf6d1cee9fa0</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -3911,18 +3911,18 @@
         </is>
       </c>
       <c r="F116" s="2" t="n">
-        <v>46235.51605324074</v>
+        <v>46260.02392361111</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>637b1ab4-9069-4ca1-8bd0-bc65ec96a983</t>
+          <t>5066f130-5e8c-4e12-bda0-31ca1a6e508b</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>43d568c5-52bc-4c5d-b7e6-9c703846aaf6</t>
+          <t>3a9f591d-8d3e-47e1-bfeb-d54fdb273c9c</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -3941,28 +3941,28 @@
         </is>
       </c>
       <c r="F117" s="2" t="n">
-        <v>46235.5177662037</v>
+        <v>46260.02563657407</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>c32ec288-9873-4599-925d-b9d9743db512</t>
+          <t>9dc6f9d1-cff9-4f1d-8cce-57fed6e15255</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>a1ddfedf-ffbd-4f50-b557-820316a3122a</t>
+          <t>48781524-dc37-4660-adff-9d43533ef266</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -3971,18 +3971,18 @@
         </is>
       </c>
       <c r="F118" s="2" t="n">
-        <v>46235.51665509259</v>
+        <v>46260.02452546296</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ce5c74cb-fa39-49de-b30a-147c6c42d5e9</t>
+          <t>c0234b04-ed82-41d3-aa30-b8d82391c07e</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>f6836f72-41ca-46a4-a558-d77e1f0eebf0</t>
+          <t>d3c084a6-e381-4a00-b199-c44b72c45a79</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4001,28 +4001,28 @@
         </is>
       </c>
       <c r="F119" s="2" t="n">
-        <v>46235.51715277778</v>
+        <v>46260.02502314815</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>911f28b3-99e6-4598-8b5e-6bb6efa6ac1d</t>
+          <t>c9073cfa-42d0-4827-b67a-49d3aa1f8c35</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>7d67b649-2b07-4661-9637-aa9890bf95dc</t>
+          <t>984f1c30-52c6-424e-bc11-911875cf29a7</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4031,23 +4031,23 @@
         </is>
       </c>
       <c r="F120" s="2" t="n">
-        <v>46235.51646990741</v>
+        <v>46260.02434027778</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>be9cc393-3dfd-4972-9f53-555c4bf01d35</t>
+          <t>9848b3dc-9ba3-4459-a27b-2a20efbb59a3</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>55423194-fdc8-4f32-839d-77611bcdfc4b</t>
+          <t>eb4dfbe2-142c-41d0-97d1-eb96e9c5681f</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4061,28 +4061,28 @@
         </is>
       </c>
       <c r="F121" s="2" t="n">
-        <v>46235.51570601852</v>
+        <v>46260.02357638889</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>048e978f-92ff-4f95-a201-7b7872017dbe</t>
+          <t>f9572bb0-6564-48b0-913d-47bcae04c83e</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>fc155d42-7dc6-4b47-8804-bc542c1c697c</t>
+          <t>3c16a4d7-a01d-4510-9883-18acb0458414</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4091,23 +4091,23 @@
         </is>
       </c>
       <c r="F122" s="2" t="n">
-        <v>46235.51715277778</v>
+        <v>46260.02502314815</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1a6f78ac-87a2-4db6-9a68-4eac3a576556</t>
+          <t>bef123db-2708-412a-b4c1-b39dd00cb388</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>96d2fc22-55b6-4269-b34b-9177573e568a</t>
+          <t>2af4e67f-a2ba-4237-8675-8f5c38b5056a</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4121,23 +4121,23 @@
         </is>
       </c>
       <c r="F123" s="2" t="n">
-        <v>46235.51771990741</v>
+        <v>46260.02559027778</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>162921e4-4b1c-4179-a7d0-2485884da188</t>
+          <t>680ed77e-59b1-48d9-8305-a8fa05646c34</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>8684a49b-c6f6-4a9d-9374-904608795ae4</t>
+          <t>39e79f91-d17c-44b4-8a29-9d3f66f36200</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -4151,28 +4151,28 @@
         </is>
       </c>
       <c r="F124" s="2" t="n">
-        <v>46235.51761574074</v>
+        <v>46260.02548611111</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>af37f063-4d22-4fde-b2da-3228a68b0aa4</t>
+          <t>1a74daed-e065-4f60-b576-9ba9f6d78441</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>850b518e-b3f3-4499-90de-e53f12082502</t>
+          <t>2a7a9a4a-d11b-4fcf-8e4b-ce08ab12433a</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4181,18 +4181,18 @@
         </is>
       </c>
       <c r="F125" s="2" t="n">
-        <v>46235.51594907408</v>
+        <v>46260.02381944445</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>06b2afa8-c2bd-4672-a0ba-5d47c047affe</t>
+          <t>2fde4d3d-685b-4961-b601-f1749dd8f2c0</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>cc0a14cf-7493-44f8-a069-694538c421aa</t>
+          <t>d8832129-bed7-41dd-8635-4db7bdc3afb1</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -4211,18 +4211,18 @@
         </is>
       </c>
       <c r="F126" s="2" t="n">
-        <v>46235.51670138889</v>
+        <v>46260.02457175926</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2c1d07f5-34ca-4f53-9353-2bf0d8bbc32a</t>
+          <t>c8fa8dae-8cac-48fd-8ad3-f0492a77ee40</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>b2762850-de9a-49c0-acfe-e3dd98758868</t>
+          <t>f0be3bff-1962-4c2b-a8bf-931211f4477b</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -4241,18 +4241,18 @@
         </is>
       </c>
       <c r="F127" s="2" t="n">
-        <v>46235.51770833333</v>
+        <v>46260.0255787037</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>93cb87dd-11f1-44aa-a5ce-a83351898f38</t>
+          <t>cd161949-f653-45c0-a92f-c192b0645821</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>fad897d1-7f43-45fa-944a-77e9b4494df6</t>
+          <t>39916282-53f8-424b-b275-93b0af32083d</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -4271,28 +4271,28 @@
         </is>
       </c>
       <c r="F128" s="2" t="n">
-        <v>46235.51584490741</v>
+        <v>46260.02371527778</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>feef73d7-55d5-458c-b2e5-208bdc158178</t>
+          <t>0e370fad-690b-4977-a853-d77f34963cea</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>fc155d42-7dc6-4b47-8804-bc542c1c697c</t>
+          <t>7759edef-05d4-45b5-8d73-26ff21a8f5f0</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4301,18 +4301,18 @@
         </is>
       </c>
       <c r="F129" s="2" t="n">
-        <v>46235.5158912037</v>
+        <v>46260.02376157408</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>b1aef16f-de0e-456b-995d-e87ba6f23d40</t>
+          <t>6577580d-9309-4d39-b626-d0ac1c1598fa</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2bf49978-fa72-4ec1-ab6d-ce3d0b4ac230</t>
+          <t>b4d5c90f-8b39-4c8a-a22f-b28fe5535f6b</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4331,18 +4331,18 @@
         </is>
       </c>
       <c r="F130" s="2" t="n">
-        <v>46235.51633101852</v>
+        <v>46260.02420138889</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1ed78672-cef8-46ee-a3cd-1c296b5cfb39</t>
+          <t>1fb15d4d-d2bb-41b1-b480-24ef3c1695a5</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>66e1ed88-0909-43c0-9c22-d4e194330a30</t>
+          <t>2febe67b-0ff0-4a57-8df5-6dff3dceebfa</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4361,23 +4361,23 @@
         </is>
       </c>
       <c r="F131" s="2" t="n">
-        <v>46235.51733796296</v>
+        <v>46260.02520833333</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>457cb8ed-733f-4f22-8f82-44218ce46456</t>
+          <t>b1111944-12c9-4519-ac25-be9ed1a2eb6d</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>3acf9e38-628c-402e-9fa3-27c0b34dd9a5</t>
+          <t>1be043c1-4206-49fb-9377-b4a0ed2b32a9</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -4391,18 +4391,18 @@
         </is>
       </c>
       <c r="F132" s="2" t="n">
-        <v>46235.5171412037</v>
+        <v>46260.02501157407</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ce7fa807-9149-4c24-8cc4-655f7218a6f6</t>
+          <t>45c12df4-bffc-481f-882c-acffd77a1e50</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>308ebee4-cf75-4efb-86cb-6aa765769eee</t>
+          <t>4d5b12de-3570-43f7-be5a-5fc9557660f5</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -4421,28 +4421,28 @@
         </is>
       </c>
       <c r="F133" s="2" t="n">
-        <v>46235.51710648148</v>
+        <v>46260.02497685186</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>f6da1441-a18a-4a62-94ef-af62d800a189</t>
+          <t>f3cec775-94c2-4814-a9cc-e0fc9070023e</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>3e945229-3185-4591-914d-55b9371d4134</t>
+          <t>42c21d36-88f7-4dd6-be02-20b2eb90c142</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -4451,23 +4451,23 @@
         </is>
       </c>
       <c r="F134" s="2" t="n">
-        <v>46235.51623842592</v>
+        <v>46260.02410879629</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>a4ebb44a-3b88-4b1d-9b10-4097b872a6c8</t>
+          <t>10039e54-f36e-4d73-904c-c51a8c376640</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>e6da211a-5cf8-4a9f-894d-c96c91a0d094</t>
+          <t>ba0a462f-c91b-4d4a-a786-03e2d12af27c</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4481,28 +4481,28 @@
         </is>
       </c>
       <c r="F135" s="2" t="n">
-        <v>46235.51719907407</v>
+        <v>46260.02506944445</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>48529f8f-6f35-4a1e-984e-93777f188391</t>
+          <t>bd299a32-b962-4d3d-bb62-cd020a459f09</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>8a3b6556-dee6-4dd2-8499-59932b7a2b84</t>
+          <t>903a9432-6229-4479-b6db-87ba9c19bc68</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -4511,28 +4511,28 @@
         </is>
       </c>
       <c r="F136" s="2" t="n">
-        <v>46235.51717592592</v>
+        <v>46260.02504629629</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>c4a1205e-b8c8-4d5a-b861-d6b0f3413e09</t>
+          <t>d89ba364-d64e-4d14-b6d4-32fc11332995</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>d3d0a42e-ef8b-4011-b9b7-ccd514c1089e</t>
+          <t>154a3ed4-2a2d-4ca9-8e50-06aaf6333c6d</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4541,23 +4541,23 @@
         </is>
       </c>
       <c r="F137" s="2" t="n">
-        <v>46235.51704861111</v>
+        <v>46260.02491898148</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>d9b5b2be-5e62-4918-a304-0c967a772c9b</t>
+          <t>84fb40c1-eeb3-401c-91b0-34df1a589321</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>55423194-fdc8-4f32-839d-77611bcdfc4b</t>
+          <t>6d1d7471-e7c7-4307-b0b8-22518b42154a</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4571,28 +4571,28 @@
         </is>
       </c>
       <c r="F138" s="2" t="n">
-        <v>46235.51591435185</v>
+        <v>46260.02378472222</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>0c5e706f-3393-46fe-b713-63ae9c7d47d6</t>
+          <t>0db358e4-deaf-4719-b788-4534b67ae9bf</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0c29877d-9f9e-434b-9220-a4d06f94a13d</t>
+          <t>d7453a46-66c7-428f-9643-2c735a03cf40</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -4601,18 +4601,18 @@
         </is>
       </c>
       <c r="F139" s="2" t="n">
-        <v>46235.51692129629</v>
+        <v>46260.02479166666</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>60dd3b79-a611-42dd-9b2c-5f4af3ead9cd</t>
+          <t>c7781076-ab6a-4132-860d-7d03443701fb</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>c6842666-a65a-4f9c-acd6-ea0c94e8b0e4</t>
+          <t>9fdad951-ff2e-4ca4-ae0b-f3e0e802e8e6</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -4631,18 +4631,18 @@
         </is>
       </c>
       <c r="F140" s="2" t="n">
-        <v>46235.51685185185</v>
+        <v>46260.02472222222</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>187fcc6a-5bd6-4cbd-919b-6f182004d5b6</t>
+          <t>49f88ad2-4560-4948-a81f-b870aec7381a</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>528e0b43-675f-4a03-bf5f-78a08c2a4203</t>
+          <t>5b996583-9ce4-4ff4-84d4-bf71fd8c0117</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -4661,18 +4661,18 @@
         </is>
       </c>
       <c r="F141" s="2" t="n">
-        <v>46235.51706018519</v>
+        <v>46260.02493055556</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>c3bd5cf7-9d99-4cf5-9664-9bd4ad92a1f5</t>
+          <t>a132d185-863a-42e1-97fd-12aa9e9b2c86</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>c7d626ed-6969-442d-ae31-381121c66db3</t>
+          <t>6dd5280e-5591-455c-a1d4-7cc15b8424b6</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -4691,18 +4691,18 @@
         </is>
       </c>
       <c r="F142" s="2" t="n">
-        <v>46235.51724537037</v>
+        <v>46260.02511574074</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ebbc05a6-f6b8-434f-bcf4-35d7928f8ecd</t>
+          <t>f9b98872-3425-4062-83e9-ff1194b7e1d8</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>b2762850-de9a-49c0-acfe-e3dd98758868</t>
+          <t>48781524-dc37-4660-adff-9d43533ef266</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -4721,28 +4721,28 @@
         </is>
       </c>
       <c r="F143" s="2" t="n">
-        <v>46235.51739583333</v>
+        <v>46260.0252662037</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>54c3c26d-2172-4472-bf6f-4c3ed5f45046</t>
+          <t>c72777c3-db1c-47ea-882c-e5c61a0bbdfd</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>c65c78c9-446b-4ee3-9a13-bd00c60f89d9</t>
+          <t>50d4198a-a465-484b-bb3f-467c0dc71f5e</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -4751,28 +4751,28 @@
         </is>
       </c>
       <c r="F144" s="2" t="n">
-        <v>46235.51686342592</v>
+        <v>46260.02473379629</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>b3dd7552-7b5c-4788-b3f7-a6c886f443fa</t>
+          <t>0da2e35c-1d7f-4abb-8628-ab6efcbf040b</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>38cf95b8-599f-4dbe-9458-9b77e202fc74</t>
+          <t>d7453a46-66c7-428f-9643-2c735a03cf40</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -4781,28 +4781,28 @@
         </is>
       </c>
       <c r="F145" s="2" t="n">
-        <v>46235.51575231482</v>
+        <v>46260.02362268518</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ff280371-c0ba-454c-90f4-251cdb95d5b5</t>
+          <t>2b80b8af-09d5-4e9f-bd63-ba72b8090fb3</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>a9555105-c0be-43b2-9c1e-7f22365601b5</t>
+          <t>fa4ef313-6b1b-4ae7-b415-bdecbcb3fe3e</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -4811,28 +4811,28 @@
         </is>
       </c>
       <c r="F146" s="2" t="n">
-        <v>46235.51778935185</v>
+        <v>46260.02565972223</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>01efdc52-d726-4cf9-a812-f6c8cdf9d2f7</t>
+          <t>06286fe1-cea4-401d-8930-61d90445f239</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>1051c4e6-abaf-4d9c-a518-d7ffebbe4f4c</t>
+          <t>50d4198a-a465-484b-bb3f-467c0dc71f5e</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -4841,18 +4841,18 @@
         </is>
       </c>
       <c r="F147" s="2" t="n">
-        <v>46235.51650462963</v>
+        <v>46260.024375</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>6507d624-e591-4acf-a7c3-7007f897bdfc</t>
+          <t>a8b49e2f-08b9-4a5e-974d-828a4f8c4788</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2bf49978-fa72-4ec1-ab6d-ce3d0b4ac230</t>
+          <t>9432ebb6-935a-449b-b05d-c19defa24cbb</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -4871,28 +4871,28 @@
         </is>
       </c>
       <c r="F148" s="2" t="n">
-        <v>46235.51678240741</v>
+        <v>46260.02465277778</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>7fcdac84-4ef5-499b-93d1-55b467bbe02f</t>
+          <t>80e0fdf6-5b7d-4d88-8aa8-da0ef5b66c16</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>8684a49b-c6f6-4a9d-9374-904608795ae4</t>
+          <t>4827461c-8604-4218-935b-97de9b45debf</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -4901,23 +4901,23 @@
         </is>
       </c>
       <c r="F149" s="2" t="n">
-        <v>46235.51741898148</v>
+        <v>46260.02528935186</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>43a3686f-4b2d-4924-a5cb-9676fe09dafd</t>
+          <t>a1297819-429a-4c21-aab6-4f0d686c0440</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>96d2fc22-55b6-4269-b34b-9177573e568a</t>
+          <t>48781524-dc37-4660-adff-9d43533ef266</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -4931,28 +4931,28 @@
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>46235.51703703704</v>
+        <v>46260.02490740741</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>dad34cb7-ff43-484b-b8eb-90c20eef70bf</t>
+          <t>e66c22fb-cd75-4aa0-b56f-f3724063906f</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>e210878d-9aeb-48b8-b43e-0950146d4e39</t>
+          <t>74532582-b900-4d1d-ad1a-54d3e0b2f77e</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -4961,28 +4961,28 @@
         </is>
       </c>
       <c r="F151" s="2" t="n">
-        <v>46235.51626157408</v>
+        <v>46260.02413194445</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>75bfe2ed-e0a7-4fc7-9580-08758f052961</t>
+          <t>17963da9-9882-43ec-930c-b3b84120d0c2</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ad5655f6-21ea-44e1-b61b-7180389ff7e4</t>
+          <t>34595e62-cdb5-4611-ae38-ae6724226212</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -4991,18 +4991,18 @@
         </is>
       </c>
       <c r="F152" s="2" t="n">
-        <v>46235.51576388889</v>
+        <v>46260.02363425926</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>c60d037d-26fc-45b7-8c29-f99790e06f85</t>
+          <t>f16cb583-26ee-4a46-b45c-a4333571ec3e</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0c29877d-9f9e-434b-9220-a4d06f94a13d</t>
+          <t>7115d65c-f83c-4f39-82f8-14e0b140364a</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -5021,18 +5021,18 @@
         </is>
       </c>
       <c r="F153" s="2" t="n">
-        <v>46235.51638888889</v>
+        <v>46260.02425925926</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>4044094a-c09e-465b-ab19-11704afbb471</t>
+          <t>fe0648b7-fa63-4793-994b-c9d1353aab91</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>f400192e-4d6f-4f9f-8b33-bcf900ded667</t>
+          <t>0214df66-56e6-43d6-ba3c-c656cd409072</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -5051,28 +5051,28 @@
         </is>
       </c>
       <c r="F154" s="2" t="n">
-        <v>46235.5162037037</v>
+        <v>46260.02407407408</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>d7c2bd7d-c247-49bf-882e-cb542aeca941</t>
+          <t>a244c7da-0397-4808-9c3a-7a47754fcbae</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0796c5fe-2105-4e74-b064-f89225821e18</t>
+          <t>435da183-3e0f-42b3-ae9c-cc48bb295930</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -5081,23 +5081,23 @@
         </is>
       </c>
       <c r="F155" s="2" t="n">
-        <v>46235.51729166666</v>
+        <v>46260.02516203704</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>bc676eae-9f5c-45ca-b80d-ac7ce8c85124</t>
+          <t>74caa11b-6197-4115-b66d-a08a5ae6088c</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>e6da211a-5cf8-4a9f-894d-c96c91a0d094</t>
+          <t>984f1c30-52c6-424e-bc11-911875cf29a7</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -5111,18 +5111,18 @@
         </is>
       </c>
       <c r="F156" s="2" t="n">
-        <v>46235.51700231482</v>
+        <v>46260.02487268519</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3bf4a9df-edff-48df-920f-82ff41da5c92</t>
+          <t>c9887297-7028-4e0f-98e3-1db3d1b94aef</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2286ba20-88d5-4e98-b15a-a4a2f55da2e5</t>
+          <t>5e05352c-24b9-4a5f-ada0-a86da6ae85fb</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -5141,18 +5141,18 @@
         </is>
       </c>
       <c r="F157" s="2" t="n">
-        <v>46235.51606481482</v>
+        <v>46260.02393518519</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>686e4df0-9fed-4631-80e9-68b9fc0a401d</t>
+          <t>6566304e-e461-49f7-b13f-ad0ee6ac98ff</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>b38830eb-c104-4bc5-91e8-9bc1235d80f0</t>
+          <t>f46b2462-0c66-4d81-a4ff-b279f7b44796</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -5171,18 +5171,18 @@
         </is>
       </c>
       <c r="F158" s="2" t="n">
-        <v>46235.51731481482</v>
+        <v>46260.02518518519</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>94e96de6-128e-42a9-84d3-9b8017430dfa</t>
+          <t>a1fea662-efc3-4d1f-ad37-da8d2689bfbf</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>4eb33a36-2364-42a1-8681-0f9ba8b082e5</t>
+          <t>b0a3f781-ef1b-4714-89dc-6e46d724f65a</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -5201,28 +5201,28 @@
         </is>
       </c>
       <c r="F159" s="2" t="n">
-        <v>46235.51711805556</v>
+        <v>46260.02498842592</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>d670096c-efa9-4fa5-85b0-1e6e8764d1d6</t>
+          <t>8a7dd69b-7639-4b99-a552-06052e8a2224</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>d40f84a3-dffa-46b0-bfff-af7f48f052ea</t>
+          <t>f2029fb7-2b7a-4d0f-8151-0bb51d7d1a1e</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -5231,18 +5231,18 @@
         </is>
       </c>
       <c r="F160" s="2" t="n">
-        <v>46235.51597222222</v>
+        <v>46260.02384259259</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>a600b277-9d97-4b4f-813e-33bef4d4324c</t>
+          <t>e492483c-49b1-41fb-8336-3401161980aa</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>839d440a-1a23-4e52-bcf0-aaf3d0e49a22</t>
+          <t>a1278a28-b565-42d8-8711-df11f4bd94a1</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -5261,18 +5261,18 @@
         </is>
       </c>
       <c r="F161" s="2" t="n">
-        <v>46235.51596064815</v>
+        <v>46260.02383101852</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>36b15c11-1db6-4736-ba30-894bab5547b0</t>
+          <t>c900a450-c88b-4bb0-a20c-535705675e4a</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>3e945229-3185-4591-914d-55b9371d4134</t>
+          <t>70ea0327-6bfa-447e-9874-93aaa1b2f4d2</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -5291,18 +5291,18 @@
         </is>
       </c>
       <c r="F162" s="2" t="n">
-        <v>46235.51660879629</v>
+        <v>46260.02447916667</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>15d57655-73ae-45ad-ac36-759e15580ccc</t>
+          <t>11fdf761-cfbe-4bac-a1c1-43a3d4a32c35</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0331a2a8-3b11-44cb-85ba-a0bb4f958be5</t>
+          <t>f0728245-7667-48c1-9d95-e88292e07edc</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -5321,18 +5321,18 @@
         </is>
       </c>
       <c r="F163" s="2" t="n">
-        <v>46235.51611111111</v>
+        <v>46260.02398148148</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>73d44ede-d8cd-410c-91af-b60b9fb059d5</t>
+          <t>5e64275e-0a85-488f-a59f-f50ba01b27d2</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>8f19ef60-b3c6-4deb-9575-b9f3a29e4090</t>
+          <t>50d4198a-a465-484b-bb3f-467c0dc71f5e</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -5351,28 +5351,28 @@
         </is>
       </c>
       <c r="F164" s="2" t="n">
-        <v>46235.51707175926</v>
+        <v>46260.02494212963</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>5f48189d-c101-4643-af76-82b2a97f5909</t>
+          <t>d305e7f7-0328-4904-b730-f12a66f8c1d8</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>f125b3f0-7ee8-411f-9efc-6527c7e1b06e</t>
+          <t>f0be3bff-1962-4c2b-a8bf-931211f4477b</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -5381,18 +5381,18 @@
         </is>
       </c>
       <c r="F165" s="2" t="n">
-        <v>46235.51648148148</v>
+        <v>46260.02435185185</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>b9c9416c-e74c-401e-91c9-6f3dd506b118</t>
+          <t>ca4ae375-04b5-4b82-82a3-e13cd71fed68</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>55423194-fdc8-4f32-839d-77611bcdfc4b</t>
+          <t>9432ebb6-935a-449b-b05d-c19defa24cbb</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -5411,18 +5411,18 @@
         </is>
       </c>
       <c r="F166" s="2" t="n">
-        <v>46235.51605324074</v>
+        <v>46260.02392361111</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>eba073a8-8376-4fd4-8991-43c97f62d3c6</t>
+          <t>e3449802-3ef5-411c-9e30-8ff59be52532</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>f4845210-5c2a-4fc4-8afe-cdecde3fc266</t>
+          <t>03959483-600c-4879-942b-25902022410d</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -5441,18 +5441,18 @@
         </is>
       </c>
       <c r="F167" s="2" t="n">
-        <v>46235.51605324074</v>
+        <v>46260.02392361111</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>54de2953-4b49-4dce-9c75-be7c3b49f6d8</t>
+          <t>59466fdb-9bbf-4b56-9cd3-39fabf2acb8d</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>7ef9145d-263a-4a30-8fcc-bf33769fcada</t>
+          <t>178dc3a5-ac00-4268-8cd4-9d9bab93c92a</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -5471,23 +5471,23 @@
         </is>
       </c>
       <c r="F168" s="2" t="n">
-        <v>46235.51694444445</v>
+        <v>46260.02481481482</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1bdf631b-4812-4c6a-bed6-69c574b90d3b</t>
+          <t>39e49963-7b57-466a-9e64-f52b97f37da6</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>4753c09d-58f1-4c9c-a01b-32798a8a7e9d</t>
+          <t>b4d5c90f-8b39-4c8a-a22f-b28fe5535f6b</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -5501,18 +5501,18 @@
         </is>
       </c>
       <c r="F169" s="2" t="n">
-        <v>46235.51663194445</v>
+        <v>46260.02450231482</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>0d31c661-b367-4aaf-a09f-cf55f1dd3fa7</t>
+          <t>632dbe38-8b48-483d-abf0-7b3a442b5d40</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>6a41a248-f2d2-4268-bc9e-ef17547cf823</t>
+          <t>af22a852-7a33-43ad-b843-7450a6faee64</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5531,18 +5531,18 @@
         </is>
       </c>
       <c r="F170" s="2" t="n">
-        <v>46235.51692129629</v>
+        <v>46260.02479166666</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>6ed5a848-b364-44c5-a6d9-f8caa90f3756</t>
+          <t>a6be2f31-e47a-45df-94c6-cf561e72f794</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>6bc31cdb-3ab1-4c66-bbc8-f2eb4e1ac3d6</t>
+          <t>9274faa9-fd95-4d89-ba77-8b3b66d3ae52</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -5561,28 +5561,28 @@
         </is>
       </c>
       <c r="F171" s="2" t="n">
-        <v>46235.51733796296</v>
+        <v>46260.02520833333</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>f24d95fb-91c7-447f-9fd8-7fb2fec7677f</t>
+          <t>66c9ffba-5c42-496b-b673-662464e15c73</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>8892a89b-9ad4-4f12-9eea-7486c41091bc</t>
+          <t>776377e7-b6f2-4c6f-89bf-4a89a9270e83</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -5591,18 +5591,18 @@
         </is>
       </c>
       <c r="F172" s="2" t="n">
-        <v>46235.51611111111</v>
+        <v>46260.02398148148</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>fad41f40-170f-466d-b61e-1a0fb2b7a8fa</t>
+          <t>2d2050b0-8310-4478-bb46-cb6b1e0252df</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>ba334fcf-a34a-4050-ad5b-fc3a3abc3bc8</t>
+          <t>2b7fc394-5b35-4a7d-993e-70e935641679</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -5621,28 +5621,28 @@
         </is>
       </c>
       <c r="F173" s="2" t="n">
-        <v>46235.51607638889</v>
+        <v>46260.02394675926</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>66ce4de8-34e3-41b0-9803-b3768625fe63</t>
+          <t>2dc9919a-9bdc-453c-83f5-2161f8858123</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>c2450c37-1faf-4512-8157-b4fde08652c4</t>
+          <t>0c1b1e0d-a4f3-4a86-8faa-c5276d9cab1e</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -5651,18 +5651,18 @@
         </is>
       </c>
       <c r="F174" s="2" t="n">
-        <v>46235.51601851852</v>
+        <v>46260.02388888889</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>00619642-32f5-45ee-99b6-da552f9a2e8d</t>
+          <t>a3bd1990-917c-42cb-a67a-52d3062478bd</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>b4bcd554-429d-4560-9171-eecf27d4d4b4</t>
+          <t>a85a9f03-5ea4-4700-a65b-a79f0fac294f</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -5681,18 +5681,18 @@
         </is>
       </c>
       <c r="F175" s="2" t="n">
-        <v>46235.51767361111</v>
+        <v>46260.02554398148</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>e8912eb8-1303-40b4-90aa-e27e8a4b662c</t>
+          <t>5b9cfd0a-1c42-4838-8af1-8a3b5883aa57</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>f5682ea1-5450-43ea-84c9-4daeb84ee1f9</t>
+          <t>9d9e4289-4025-447e-bb52-2522a4afca57</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -5711,28 +5711,28 @@
         </is>
       </c>
       <c r="F176" s="2" t="n">
-        <v>46235.51673611111</v>
+        <v>46260.02460648148</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>fbd5204a-84bf-4c59-b900-bb39d53b340c</t>
+          <t>36afae4e-b5ea-4f24-b9ec-e7a4d851d758</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>7ace690d-631f-4ca4-9072-4cbbb8ec8aba</t>
+          <t>984f1c30-52c6-424e-bc11-911875cf29a7</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -5741,18 +5741,18 @@
         </is>
       </c>
       <c r="F177" s="2" t="n">
-        <v>46235.5171875</v>
+        <v>46260.02505787037</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>e3a911e8-5ad2-4c90-a038-7edac0e4cea1</t>
+          <t>b10e32c6-2d23-4283-ac2a-37bf16759b80</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>c51dd9c0-f03a-4383-b846-cb163e9cb4ba</t>
+          <t>03959483-600c-4879-942b-25902022410d</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -5771,18 +5771,18 @@
         </is>
       </c>
       <c r="F178" s="2" t="n">
-        <v>46235.51719907407</v>
+        <v>46260.02506944445</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>3186ab30-f3ca-49fc-9e7f-cdcbf5a1806b</t>
+          <t>2dc7216f-0743-4e1f-bac6-0e98386b04d4</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>424d4004-6fbb-426b-81d2-0216c2bf29fc</t>
+          <t>39e79f91-d17c-44b4-8a29-9d3f66f36200</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5801,18 +5801,18 @@
         </is>
       </c>
       <c r="F179" s="2" t="n">
-        <v>46235.51603009259</v>
+        <v>46260.02390046296</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>db9e2970-440f-4707-9b28-958068a7e47e</t>
+          <t>0f66a7e1-2666-4577-a65a-5525eeffaaaa</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>0331a2a8-3b11-44cb-85ba-a0bb4f958be5</t>
+          <t>03959483-600c-4879-942b-25902022410d</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -5831,18 +5831,18 @@
         </is>
       </c>
       <c r="F180" s="2" t="n">
-        <v>46235.51733796296</v>
+        <v>46260.02520833333</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>62d640b9-c6f8-4d97-86ab-f37dd0bfe11a</t>
+          <t>8888f9b7-c56b-40d1-b7a2-75bd1c368e5d</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>7848690a-f055-4234-80f1-e4b2ea7be344</t>
+          <t>9abe646f-9247-4c8f-8c1d-509abe328744</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -5861,18 +5861,18 @@
         </is>
       </c>
       <c r="F181" s="2" t="n">
-        <v>46235.51700231482</v>
+        <v>46260.02487268519</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>65ad6e2c-718b-4440-abb0-d89f50135a23</t>
+          <t>0998412b-adde-4e3e-9fed-4dd8619cabbb</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ba260fd8-7e47-43f3-8e00-c47c3bc12abe</t>
+          <t>a8f0020c-6daa-4fe6-8f45-df1383ad979a</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -5891,18 +5891,18 @@
         </is>
       </c>
       <c r="F182" s="2" t="n">
-        <v>46235.51689814815</v>
+        <v>46260.02476851852</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>41ba310d-109b-4f3e-8316-e01fdbf0f7f7</t>
+          <t>3d71256c-dbaf-44da-bf23-ae21eb314cda</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>7ef9145d-263a-4a30-8fcc-bf33769fcada</t>
+          <t>4d5b12de-3570-43f7-be5a-5fc9557660f5</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -5921,23 +5921,23 @@
         </is>
       </c>
       <c r="F183" s="2" t="n">
-        <v>46235.51760416666</v>
+        <v>46260.02547453704</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>463fb9bb-abfb-4332-bd48-c7f499ad880a</t>
+          <t>790bb7a5-7ae6-4124-9337-012f17201be2</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>43d568c5-52bc-4c5d-b7e6-9c703846aaf6</t>
+          <t>0d43b730-1055-43fb-a8e0-51a89c415253</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -5951,18 +5951,18 @@
         </is>
       </c>
       <c r="F184" s="2" t="n">
-        <v>46235.51578703704</v>
+        <v>46260.02365740741</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>9856aa97-67e9-4563-ab40-f2ada8d55edc</t>
+          <t>dcc64672-dec0-4e6b-a421-9743325348ae</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>8892a89b-9ad4-4f12-9eea-7486c41091bc</t>
+          <t>2913e0e0-acee-4aaa-9356-eeefbcedc009</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -5981,18 +5981,18 @@
         </is>
       </c>
       <c r="F185" s="2" t="n">
-        <v>46235.51659722222</v>
+        <v>46260.02446759259</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>182f39b9-d0b4-4297-8955-20f9c65c0f95</t>
+          <t>72ba6791-2c7e-40f3-8600-48a0b958c0e7</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>92c7e79f-a989-4305-ba48-2af36ce8d6d6</t>
+          <t>575ebed8-a5ac-49dc-b418-6417a95748a0</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6011,18 +6011,18 @@
         </is>
       </c>
       <c r="F186" s="2" t="n">
-        <v>46235.51579861111</v>
+        <v>46260.02366898148</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1805422e-b2ef-42b4-a4af-26f4fca7e005</t>
+          <t>32249804-ffc5-4283-acfb-90ff9b945c4a</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>bcfafb41-c981-497c-b534-9959fcec4b9b</t>
+          <t>b4d5c90f-8b39-4c8a-a22f-b28fe5535f6b</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -6041,28 +6041,28 @@
         </is>
       </c>
       <c r="F187" s="2" t="n">
-        <v>46235.51697916666</v>
+        <v>46260.02484953704</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>a08be7b5-a602-4405-95cc-016cc6e20a7c</t>
+          <t>330859f4-8e65-41a2-83f2-8d62ede7da86</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>d3d0a42e-ef8b-4011-b9b7-ccd514c1089e</t>
+          <t>b9c0327f-d2a9-4e00-9edc-0c54a17063ac</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -6071,18 +6071,18 @@
         </is>
       </c>
       <c r="F188" s="2" t="n">
-        <v>46235.51709490741</v>
+        <v>46260.02496527778</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>7bf79c23-c8b0-4458-8a1a-043698d5c83e</t>
+          <t>7ee499cb-c143-47b4-b533-9d96cf4507ea</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>69b84e67-3b6f-43f6-be94-61afd6b646f9</t>
+          <t>1be043c1-4206-49fb-9377-b4a0ed2b32a9</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -6101,18 +6101,18 @@
         </is>
       </c>
       <c r="F189" s="2" t="n">
-        <v>46235.51678240741</v>
+        <v>46260.02465277778</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ae63dbd2-8c55-4c41-b95f-7b48a4e8f78f</t>
+          <t>2cbd5b1f-e5cf-4ce7-ad6c-6f03c6740c5c</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>1779b6fe-21b9-49f3-a23b-0b838095bc4a</t>
+          <t>1be043c1-4206-49fb-9377-b4a0ed2b32a9</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -6131,18 +6131,18 @@
         </is>
       </c>
       <c r="F190" s="2" t="n">
-        <v>46235.51640046296</v>
+        <v>46260.02427083333</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>71a7bb02-49c5-4f0e-bd8f-bdaf63292a47</t>
+          <t>591ea5f0-80b0-4ae2-bb84-ad181e97a629</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>c8ba352f-ba91-4913-975f-71f16968349b</t>
+          <t>af22a852-7a33-43ad-b843-7450a6faee64</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6161,18 +6161,18 @@
         </is>
       </c>
       <c r="F191" s="2" t="n">
-        <v>46235.51738425926</v>
+        <v>46260.02525462963</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>8cb3ac2f-9cb8-4674-b0f4-6e79b0799d34</t>
+          <t>5ec8351a-510f-4c53-b0b5-4dc37f1f3f35</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>0a4650bd-4472-4b05-a73d-ab41d73c93d9</t>
+          <t>2b7fc394-5b35-4a7d-993e-70e935641679</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6191,18 +6191,18 @@
         </is>
       </c>
       <c r="F192" s="2" t="n">
-        <v>46235.5171875</v>
+        <v>46260.02505787037</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>49b71aa1-0150-40a4-9158-179830a54c01</t>
+          <t>6c17bb82-4d4c-4b69-8065-3fb689538cba</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>edf33408-32f0-4023-8f23-d2976b8c6f24</t>
+          <t>edad974c-47fc-4693-b9ec-e9da03b5ea56</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -6221,18 +6221,18 @@
         </is>
       </c>
       <c r="F193" s="2" t="n">
-        <v>46235.51658564815</v>
+        <v>46260.02445601852</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>5e925769-b6c1-46c1-a2d0-b8f258ea08f1</t>
+          <t>ee755f63-31bd-4b94-bd2e-23b6a84f9361</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>e210878d-9aeb-48b8-b43e-0950146d4e39</t>
+          <t>903a9432-6229-4479-b6db-87ba9c19bc68</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6251,23 +6251,23 @@
         </is>
       </c>
       <c r="F194" s="2" t="n">
-        <v>46235.51659722222</v>
+        <v>46260.02446759259</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>e7d9f6e7-f9a0-4a13-8e48-15d9776d6c92</t>
+          <t>03d81e66-659c-4bb1-906a-cb8df8729820</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>e3d9247e-ea45-42d7-8201-79321ec44c55</t>
+          <t>2ea2e1c1-fe6c-4ea1-b686-e385ea34fce0</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -6281,23 +6281,23 @@
         </is>
       </c>
       <c r="F195" s="2" t="n">
-        <v>46235.51740740741</v>
+        <v>46260.02527777778</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>171dd680-728f-4c26-8965-43326045a039</t>
+          <t>30d9806d-2326-4634-980e-405c18a64d3b</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>8a3b6556-dee6-4dd2-8499-59932b7a2b84</t>
+          <t>a85a9f03-5ea4-4700-a65b-a79f0fac294f</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -6311,23 +6311,23 @@
         </is>
       </c>
       <c r="F196" s="2" t="n">
-        <v>46235.51678240741</v>
+        <v>46260.02465277778</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>deac62cb-fdea-4e88-8a3d-28bec287e4c3</t>
+          <t>243e8a1b-f856-4c88-a804-9b36950bdde3</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>3fb7fd85-868b-44a1-9a49-cc8a0c6772b1</t>
+          <t>b0a3f781-ef1b-4714-89dc-6e46d724f65a</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -6341,28 +6341,28 @@
         </is>
       </c>
       <c r="F197" s="2" t="n">
-        <v>46235.51761574074</v>
+        <v>46260.02548611111</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>6a6aeeed-c0df-47b8-ac3a-e173d018d66a</t>
+          <t>f8c3d59b-fec9-40f7-bb3e-33ffd7c2de61</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>7d67b649-2b07-4661-9637-aa9890bf95dc</t>
+          <t>5e5594a5-243d-4fa3-8baa-f8c16db7ddf9</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -6371,18 +6371,18 @@
         </is>
       </c>
       <c r="F198" s="2" t="n">
-        <v>46235.51736111111</v>
+        <v>46260.02523148148</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>f06d8ef0-a1f1-4823-bb0c-124482513808</t>
+          <t>88002f93-1a4e-4e1b-920e-1032b2e8d97f</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>f400192e-4d6f-4f9f-8b33-bcf900ded667</t>
+          <t>0566f9df-30ab-44ee-81c2-56f47a689fbc</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -6401,28 +6401,28 @@
         </is>
       </c>
       <c r="F199" s="2" t="n">
-        <v>46235.51576388889</v>
+        <v>46260.02363425926</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>a21a7a46-4d23-449f-820d-13458fb9c0df</t>
+          <t>29129028-1a42-4ac9-9e45-8e3d64888cde</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>d3529462-3595-46e5-8c31-5302aa767759</t>
+          <t>c4e97974-3a35-4cf4-9ba0-21fade7cfdd9</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -6431,28 +6431,28 @@
         </is>
       </c>
       <c r="F200" s="2" t="n">
-        <v>46235.51678240741</v>
+        <v>46260.02465277778</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>d9045728-b929-4451-a481-a24009bb88f6</t>
+          <t>b184f775-4c69-4d9b-a60b-0bcecfd8a1df</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2286ba20-88d5-4e98-b15a-a4a2f55da2e5</t>
+          <t>984f1c30-52c6-424e-bc11-911875cf29a7</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -6461,28 +6461,28 @@
         </is>
       </c>
       <c r="F201" s="2" t="n">
-        <v>46235.51767361111</v>
+        <v>46260.02554398148</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>0b6d9505-9251-4def-9dbe-4643c557594d</t>
+          <t>c9ffaf8c-832a-4a63-b252-597c41df28a0</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>7248dc99-ee9f-4476-bf41-52006d8325f3</t>
+          <t>f53d985f-2219-497c-93c4-97f25f762f7d</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -6491,18 +6491,18 @@
         </is>
       </c>
       <c r="F202" s="2" t="n">
-        <v>46235.51612268519</v>
+        <v>46260.02399305555</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>b41fb19f-4ca6-442e-8e8a-7dc1aca4994e</t>
+          <t>d88f4328-cc5c-4398-822c-08ae811678b5</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>3fb7fd85-868b-44a1-9a49-cc8a0c6772b1</t>
+          <t>483718f8-e416-41cd-904d-7a237019c393</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -6521,28 +6521,28 @@
         </is>
       </c>
       <c r="F203" s="2" t="n">
-        <v>46235.51603009259</v>
+        <v>46260.02390046296</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>850ee86b-e7ca-4313-977a-c247ddd380db</t>
+          <t>890f27d1-4c29-4b84-a686-06597dd021ce</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>4ab211f3-603b-4e93-8c83-18a4219540ff</t>
+          <t>ac1c07c9-3e8b-46e4-a18f-755c6bcf1400</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -6551,18 +6551,18 @@
         </is>
       </c>
       <c r="F204" s="2" t="n">
-        <v>46235.5175</v>
+        <v>46260.02537037037</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>d1581a45-0f69-4c9b-95a5-f55922da2bea</t>
+          <t>98cb6dc7-3328-40a6-83fe-9538cc784e3f</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>4b177a79-1e3b-4908-a573-43c662c3a15b</t>
+          <t>435da183-3e0f-42b3-ae9c-cc48bb295930</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -6581,28 +6581,28 @@
         </is>
       </c>
       <c r="F205" s="2" t="n">
-        <v>46235.51733796296</v>
+        <v>46260.02520833333</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>9cfdd88f-d135-4e8a-b011-7306fbbd0411</t>
+          <t>eb519382-7090-4454-9588-0337dfd6c367</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>7ace690d-631f-4ca4-9072-4cbbb8ec8aba</t>
+          <t>16339253-1399-472f-b0c8-52b51b14ff5d</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -6611,18 +6611,18 @@
         </is>
       </c>
       <c r="F206" s="2" t="n">
-        <v>46235.51645833333</v>
+        <v>46260.0243287037</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>3f65e80b-489f-475c-bfb7-de284e827b7e</t>
+          <t>7d95cea9-22cb-4fe2-99ff-4ac524af1e8d</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>69b84e67-3b6f-43f6-be94-61afd6b646f9</t>
+          <t>f46832c4-0044-47b6-928b-f39ddfffd89d</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6641,28 +6641,28 @@
         </is>
       </c>
       <c r="F207" s="2" t="n">
-        <v>46235.51690972222</v>
+        <v>46260.02478009259</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>5f0bcc18-c6ab-41e0-ae35-782aa4d8d1ab</t>
+          <t>dec61a7b-8d30-442a-821c-009753b25714</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>82fed8e5-31da-4832-a85b-fcc0b091695f</t>
+          <t>b9c0327f-d2a9-4e00-9edc-0c54a17063ac</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -6671,28 +6671,28 @@
         </is>
       </c>
       <c r="F208" s="2" t="n">
-        <v>46235.51668981482</v>
+        <v>46260.02456018519</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>e0b0d01e-4f0d-4c63-b3b8-0d68a7aa7b03</t>
+          <t>3a1828f2-1ec7-45ff-bb81-acb28271c5ed</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>d469e12d-956a-4e2a-89e1-75db9f7448cb</t>
+          <t>74dcaab0-ca92-4995-a856-2eec8c712296</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -6701,18 +6701,18 @@
         </is>
       </c>
       <c r="F209" s="2" t="n">
-        <v>46235.51585648148</v>
+        <v>46260.02372685185</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>eda40ab2-9776-42a6-95ef-4695fb08230e</t>
+          <t>86ed8b9b-3d2d-4c2e-a865-a1ba2d4dfab2</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>d3529462-3595-46e5-8c31-5302aa767759</t>
+          <t>fa6db45d-639a-4ebc-bff1-f5971e108081</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -6731,18 +6731,18 @@
         </is>
       </c>
       <c r="F210" s="2" t="n">
-        <v>46235.51723379629</v>
+        <v>46260.02510416666</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>15a9fd2b-7c39-46c0-8add-3d8afe1fb14d</t>
+          <t>b2f8829b-eae0-4f4c-aa0d-f2e11caac0bd</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>a02a5149-5005-4b03-84f6-81416d09c2c2</t>
+          <t>6e932cf0-f369-4379-8e7e-1913eb40bf4a</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -6761,18 +6761,18 @@
         </is>
       </c>
       <c r="F211" s="2" t="n">
-        <v>46235.51773148148</v>
+        <v>46260.02560185185</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>976cee9f-0da3-4d48-bfac-6df30170fb40</t>
+          <t>93579333-3bc2-47f0-9d1f-ef0e46164b68</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>e3d9247e-ea45-42d7-8201-79321ec44c55</t>
+          <t>7759edef-05d4-45b5-8d73-26ff21a8f5f0</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -6791,18 +6791,18 @@
         </is>
       </c>
       <c r="F212" s="2" t="n">
-        <v>46235.51596064815</v>
+        <v>46260.02383101852</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>52b181d0-5f2d-4581-b356-84f9700d9bc1</t>
+          <t>3f72973a-c40d-48bc-b43a-f4f7d017d38c</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>424d4004-6fbb-426b-81d2-0216c2bf29fc</t>
+          <t>1be043c1-4206-49fb-9377-b4a0ed2b32a9</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -6821,18 +6821,18 @@
         </is>
       </c>
       <c r="F213" s="2" t="n">
-        <v>46235.51699074074</v>
+        <v>46260.02486111111</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>22213db8-40c8-4252-be79-0abcffd093ea</t>
+          <t>323ab9c0-8511-4448-bd62-18dd13e33bb1</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>c54622a9-766f-4b0a-9ca6-107e30205d18</t>
+          <t>fb408916-cd92-43cf-b606-fde8cecf8d71</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -6851,18 +6851,18 @@
         </is>
       </c>
       <c r="F214" s="2" t="n">
-        <v>46235.51634259259</v>
+        <v>46260.02421296296</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2efc1c2a-6fca-41fe-be91-283c64f07870</t>
+          <t>8971ec4e-e42e-41d4-9c86-2399eea4f147</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>c51dd9c0-f03a-4383-b846-cb163e9cb4ba</t>
+          <t>b4417c0f-3d7e-4f01-b12c-b52af4b2ece7</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -6881,18 +6881,18 @@
         </is>
       </c>
       <c r="F215" s="2" t="n">
-        <v>46235.51743055556</v>
+        <v>46260.02530092592</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>356a99bf-24d6-4c64-bb9a-0a090f12664a</t>
+          <t>1e151630-1f7b-4bbe-a1e0-cd90336667fb</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2cc991a9-4b6b-461e-a079-f79e85b31887</t>
+          <t>59745190-f939-4fbf-b47f-779560330b91</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6911,28 +6911,28 @@
         </is>
       </c>
       <c r="F216" s="2" t="n">
-        <v>46235.51585648148</v>
+        <v>46260.02372685185</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>efa48675-48fb-450e-bc8c-4ba240fe9307</t>
+          <t>3639d38e-8960-46b3-9db0-3d59a68330f3</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>217d8d97-267f-42b8-b0c4-0e9892150141</t>
+          <t>2913e0e0-acee-4aaa-9356-eeefbcedc009</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -6941,28 +6941,28 @@
         </is>
       </c>
       <c r="F217" s="2" t="n">
-        <v>46235.5168287037</v>
+        <v>46260.02469907407</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>7b65a35f-c7de-4806-b159-ef76e97a277b</t>
+          <t>8e9a9286-af88-4905-8552-330541ba5e05</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>3acf9e38-628c-402e-9fa3-27c0b34dd9a5</t>
+          <t>eb4dfbe2-142c-41d0-97d1-eb96e9c5681f</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -6971,18 +6971,18 @@
         </is>
       </c>
       <c r="F218" s="2" t="n">
-        <v>46235.51708333333</v>
+        <v>46260.0249537037</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>7bf995e9-8dbd-4f6b-9046-de5bfcb6fe71</t>
+          <t>605946bc-aaf8-4401-96be-0b6d1b2d6aff</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>f0b2aa71-8809-4d4a-a04f-dfcb3b546765</t>
+          <t>6469a201-c598-4bc6-b451-765e0d37845d</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -7001,28 +7001,28 @@
         </is>
       </c>
       <c r="F219" s="2" t="n">
-        <v>46235.51652777778</v>
+        <v>46260.02439814815</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>41000dd8-8fed-476b-8674-5bc14c92db70</t>
+          <t>1f73cce5-b4ec-49b8-b6d6-56f3802202b5</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>b38830eb-c104-4bc5-91e8-9bc1235d80f0</t>
+          <t>6d1d7471-e7c7-4307-b0b8-22518b42154a</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -7031,18 +7031,18 @@
         </is>
       </c>
       <c r="F220" s="2" t="n">
-        <v>46235.51614583333</v>
+        <v>46260.0240162037</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>dcf04e11-5d32-43ff-8469-4723a6d530b5</t>
+          <t>102548d2-7a08-4ddf-aaa7-40c8e35771f0</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>0c29877d-9f9e-434b-9220-a4d06f94a13d</t>
+          <t>0d11a5cd-c7c9-4a02-8f7e-13967a601011</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -7061,28 +7061,28 @@
         </is>
       </c>
       <c r="F221" s="2" t="n">
-        <v>46235.51675925926</v>
+        <v>46260.02462962963</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>cf3391ac-c4bd-48df-9d0b-59a27981b79b</t>
+          <t>8e3ad806-e045-4347-9f7b-d8eb354a4511</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>8ecf5ef6-2f73-4522-8462-4b71c8951bbb</t>
+          <t>1ac47239-beb3-4f9a-b7a1-f1b6d57b540d</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -7091,28 +7091,28 @@
         </is>
       </c>
       <c r="F222" s="2" t="n">
-        <v>46235.51743055556</v>
+        <v>46260.02530092592</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>7f2e8241-5130-48f4-9eb3-165a8e2c26f1</t>
+          <t>df32b124-13a9-4545-95dd-292b210d2b37</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>f08374c2-d025-4414-b22f-ec278b0fcd13</t>
+          <t>70ea0327-6bfa-447e-9874-93aaa1b2f4d2</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -7121,28 +7121,28 @@
         </is>
       </c>
       <c r="F223" s="2" t="n">
-        <v>46235.51667824074</v>
+        <v>46260.02454861111</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>e84c8d88-05a2-40a4-9cf4-534cbf387ee9</t>
+          <t>0b150026-c482-49f9-8d1d-42544baa0310</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>b38830eb-c104-4bc5-91e8-9bc1235d80f0</t>
+          <t>cc734625-0fd5-4c45-9e15-119fe2d63e41</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -7151,23 +7151,23 @@
         </is>
       </c>
       <c r="F224" s="2" t="n">
-        <v>46235.51665509259</v>
+        <v>46260.02452546296</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>cdf557f9-2431-4e5a-9d56-72e320ecd186</t>
+          <t>7b5b2bcb-be58-484c-a2de-135d94bf51be</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>d3529462-3595-46e5-8c31-5302aa767759</t>
+          <t>2527d7bf-bd61-44ad-aa0c-b305868e62d3</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -7181,23 +7181,23 @@
         </is>
       </c>
       <c r="F225" s="2" t="n">
-        <v>46235.51667824074</v>
+        <v>46260.02454861111</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>e6b0ca30-cad4-44eb-9e65-c64f97e7a816</t>
+          <t>2c812ff6-02d4-49be-897a-8ffd1986ce58</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>c7d626ed-6969-442d-ae31-381121c66db3</t>
+          <t>de51a2d1-45e9-4794-91de-bf6d1cee9fa0</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -7211,18 +7211,18 @@
         </is>
       </c>
       <c r="F226" s="2" t="n">
-        <v>46235.51738425926</v>
+        <v>46260.02525462963</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>881a1d45-db07-4eed-b81d-db5e6e7463f9</t>
+          <t>114aed24-ffad-4183-a329-d461857e2a21</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>d469e12d-956a-4e2a-89e1-75db9f7448cb</t>
+          <t>6d1d7471-e7c7-4307-b0b8-22518b42154a</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -7241,18 +7241,18 @@
         </is>
       </c>
       <c r="F227" s="2" t="n">
-        <v>46235.5168287037</v>
+        <v>46260.02469907407</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>571483f1-6429-4f00-8619-06de679d0377</t>
+          <t>c213ed1e-6476-47ea-b208-06cf28dbcd64</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>dffd8ecf-ca39-4aa8-b63f-5e476be76235</t>
+          <t>10b429ae-1867-484b-9708-7a09429e758c</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -7271,18 +7271,18 @@
         </is>
       </c>
       <c r="F228" s="2" t="n">
-        <v>46235.51689814815</v>
+        <v>46260.02476851852</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>8bb5bbcc-4400-41a0-b152-f5c007a4ea6e</t>
+          <t>b95b36f7-d37a-4ff6-a62d-5b41d1ec6f93</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2286ba20-88d5-4e98-b15a-a4a2f55da2e5</t>
+          <t>c6a89594-1770-4a84-9934-0a239846819d</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -7301,18 +7301,18 @@
         </is>
       </c>
       <c r="F229" s="2" t="n">
-        <v>46235.51675925926</v>
+        <v>46260.02462962963</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1fab9aab-4929-4271-9f90-c77f0be674b0</t>
+          <t>9d91eb34-ccc3-4448-97e0-c2dd27045417</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>b7a19cf0-0919-4c00-b128-dcff53eacaba</t>
+          <t>b0a3f781-ef1b-4714-89dc-6e46d724f65a</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -7331,18 +7331,18 @@
         </is>
       </c>
       <c r="F230" s="2" t="n">
-        <v>46235.51695601852</v>
+        <v>46260.02482638889</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>a92b85ab-b17d-4055-a7cc-cb2dceca4825</t>
+          <t>f5ecaa68-779c-4b20-a1a3-78edbb39fc79</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>9ec9f95e-1468-4c4f-a006-fca793e34aa1</t>
+          <t>9d9e4289-4025-447e-bb52-2522a4afca57</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -7361,18 +7361,18 @@
         </is>
       </c>
       <c r="F231" s="2" t="n">
-        <v>46235.51756944445</v>
+        <v>46260.02543981482</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>4e3f2471-b8dc-4eae-87a2-b7fe312d030c</t>
+          <t>0fd9a2ef-1011-4b8b-b6ee-067e7c06ef33</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>366e31e3-8bb0-4d12-ab99-a13519befbb3</t>
+          <t>42bbf194-0cb7-44aa-bbae-09280e0d27c8</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -7391,28 +7391,28 @@
         </is>
       </c>
       <c r="F232" s="2" t="n">
-        <v>46235.51583333333</v>
+        <v>46260.0237037037</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>8c2b7b69-f2b0-40aa-bbf1-34a79518170e</t>
+          <t>16e357cd-8c5b-487a-aefc-0c6839bc2530</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>366e31e3-8bb0-4d12-ab99-a13519befbb3</t>
+          <t>6dd5280e-5591-455c-a1d4-7cc15b8424b6</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -7421,18 +7421,18 @@
         </is>
       </c>
       <c r="F233" s="2" t="n">
-        <v>46235.51623842592</v>
+        <v>46260.02410879629</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>eb26c6ec-1d64-40d4-bf7a-7b91c6aed733</t>
+          <t>f510e45d-eb9a-4b15-87da-1be2a5ee7cbe</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>404eeff5-1117-491d-b2b5-3c343df24dfc</t>
+          <t>0d43b730-1055-43fb-a8e0-51a89c415253</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -7451,18 +7451,18 @@
         </is>
       </c>
       <c r="F234" s="2" t="n">
-        <v>46235.51633101852</v>
+        <v>46260.02420138889</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1d9bb8ca-0807-4d10-9776-1e4e4f2c6152</t>
+          <t>aea10ba8-df4b-4071-9d0b-17b55d121193</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>7d67b649-2b07-4661-9637-aa9890bf95dc</t>
+          <t>e77d4500-ab6b-444e-bd4a-ce9e608a4669</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -7481,18 +7481,18 @@
         </is>
       </c>
       <c r="F235" s="2" t="n">
-        <v>46235.51763888889</v>
+        <v>46260.02550925926</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>8e876a2a-de1a-498b-aaab-d57d32d22653</t>
+          <t>8c7f1603-2a3a-4f5f-bb60-9ef49d94f7e2</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>528e0b43-675f-4a03-bf5f-78a08c2a4203</t>
+          <t>6469a201-c598-4bc6-b451-765e0d37845d</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -7511,18 +7511,18 @@
         </is>
       </c>
       <c r="F236" s="2" t="n">
-        <v>46235.51596064815</v>
+        <v>46260.02383101852</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>7082683f-1e4f-4031-8ab7-274aea94de0e</t>
+          <t>f2fb88f9-f7cc-4332-823b-79974c4818ce</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>65744c9b-e37c-4ecb-9591-e99e379e7524</t>
+          <t>f46b2462-0c66-4d81-a4ff-b279f7b44796</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -7541,18 +7541,18 @@
         </is>
       </c>
       <c r="F237" s="2" t="n">
-        <v>46235.51613425926</v>
+        <v>46260.02400462963</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>502ec124-252f-4981-8dcd-8204a99cb19b</t>
+          <t>6ca74723-938e-4f09-afe6-9df02e444cd4</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2cc991a9-4b6b-461e-a079-f79e85b31887</t>
+          <t>154a3ed4-2a2d-4ca9-8e50-06aaf6333c6d</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -7571,18 +7571,18 @@
         </is>
       </c>
       <c r="F238" s="2" t="n">
-        <v>46235.51615740741</v>
+        <v>46260.02402777778</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>a5f2f276-4631-43d7-8cfc-6d9a7ff1e71b</t>
+          <t>de8759e6-19a3-4109-af80-d17177b41bbc</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>f6836f72-41ca-46a4-a558-d77e1f0eebf0</t>
+          <t>d7453a46-66c7-428f-9643-2c735a03cf40</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -7601,18 +7601,18 @@
         </is>
       </c>
       <c r="F239" s="2" t="n">
-        <v>46235.51693287037</v>
+        <v>46260.02480324074</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>dd56ea58-99a8-4ec0-ad75-55705ef2308f</t>
+          <t>c5b47817-38e9-4cf2-a708-33ec3c5b4074</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>3e945229-3185-4591-914d-55b9371d4134</t>
+          <t>28b67771-a6f7-4b9c-9ab7-060306d37d94</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -7631,18 +7631,18 @@
         </is>
       </c>
       <c r="F240" s="2" t="n">
-        <v>46235.51726851852</v>
+        <v>46260.02513888889</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>54e8a7d9-16f7-4995-bfbe-9bcf56646e53</t>
+          <t>952108f0-092c-43e8-8e5c-d596bbe82f20</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>27bb84a0-a253-4b7a-9ae2-49660adc0b92</t>
+          <t>2527d7bf-bd61-44ad-aa0c-b305868e62d3</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -7661,28 +7661,28 @@
         </is>
       </c>
       <c r="F241" s="2" t="n">
-        <v>46235.51716435186</v>
+        <v>46260.02503472222</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>6e9b92e9-3002-42fc-b672-96fc36659c83</t>
+          <t>483e1304-ca84-4fde-84a7-e3d4fec4a873</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>b38830eb-c104-4bc5-91e8-9bc1235d80f0</t>
+          <t>0214df66-56e6-43d6-ba3c-c656cd409072</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -7691,18 +7691,18 @@
         </is>
       </c>
       <c r="F242" s="2" t="n">
-        <v>46235.51765046296</v>
+        <v>46260.02552083333</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>c55d1076-2e12-488f-8c20-d5ca2872ecab</t>
+          <t>01929a85-3870-4187-b9ca-4697db02ee0a</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>0c29877d-9f9e-434b-9220-a4d06f94a13d</t>
+          <t>24aed73a-55a4-4ad2-961a-fa5d278c3bc3</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -7721,18 +7721,18 @@
         </is>
       </c>
       <c r="F243" s="2" t="n">
-        <v>46235.51653935185</v>
+        <v>46260.02440972222</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>5dfae67c-ca0d-4749-89b6-d260820d44f8</t>
+          <t>18e40212-6d25-44eb-9918-23dbc28fd9bd</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>24f5aafd-9747-4ddb-b372-9ae82a1015d0</t>
+          <t>aa4952cc-be1c-43ef-8fbe-0a28811e57bc</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -7751,28 +7751,28 @@
         </is>
       </c>
       <c r="F244" s="2" t="n">
-        <v>46235.51659722222</v>
+        <v>46260.02446759259</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>a24bafed-d77b-4ddb-902c-65238268c60a</t>
+          <t>ab910a6c-7e74-464e-a2a1-dea3e7919b2d</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>f08374c2-d025-4414-b22f-ec278b0fcd13</t>
+          <t>4d5b12de-3570-43f7-be5a-5fc9557660f5</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -7781,23 +7781,23 @@
         </is>
       </c>
       <c r="F245" s="2" t="n">
-        <v>46235.5158912037</v>
+        <v>46260.02376157408</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>8f6ae945-c77e-4a79-b0bb-0dbcf3927e1b</t>
+          <t>69ff9ec4-9cb9-4b7d-aec3-108d4f42f8e7</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>404eeff5-1117-491d-b2b5-3c343df24dfc</t>
+          <t>10b429ae-1867-484b-9708-7a09429e758c</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -7811,18 +7811,18 @@
         </is>
       </c>
       <c r="F246" s="2" t="n">
-        <v>46235.51614583333</v>
+        <v>46260.0240162037</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>b8d30466-431e-4eb7-8db4-cda2796e7888</t>
+          <t>15059024-5fbb-4a49-8934-406ca6c795cb</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>308ebee4-cf75-4efb-86cb-6aa765769eee</t>
+          <t>1ac47239-beb3-4f9a-b7a1-f1b6d57b540d</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -7841,28 +7841,28 @@
         </is>
       </c>
       <c r="F247" s="2" t="n">
-        <v>46235.51736111111</v>
+        <v>46260.02523148148</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>7fc22adb-7452-427a-b094-2b8d8a4812c0</t>
+          <t>1e32560d-c489-4251-bda4-a81ef7f86a37</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>79e13ac4-50c3-4d42-ac3b-cd01498a2a5a</t>
+          <t>0d11a5cd-c7c9-4a02-8f7e-13967a601011</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -7871,18 +7871,18 @@
         </is>
       </c>
       <c r="F248" s="2" t="n">
-        <v>46235.51701388889</v>
+        <v>46260.02488425926</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>b9882150-fe74-460d-ae0a-b6d5d18d4943</t>
+          <t>c7d6ce22-7f77-4c48-8e9a-7efab2b8a462</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2e9ef7de-9919-42d3-bda6-3521e6b0363c</t>
+          <t>f53d985f-2219-497c-93c4-97f25f762f7d</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -7901,18 +7901,18 @@
         </is>
       </c>
       <c r="F249" s="2" t="n">
-        <v>46235.51655092592</v>
+        <v>46260.02442129629</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>28e7e3b9-975a-4d85-b1ab-acf5d5ea87fa</t>
+          <t>e27097cd-c2ba-4811-9127-244e7ef6be85</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>92c7e79f-a989-4305-ba48-2af36ce8d6d6</t>
+          <t>027f5e4d-00c8-4543-847e-dee93a96d0d3</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -7931,18 +7931,18 @@
         </is>
       </c>
       <c r="F250" s="2" t="n">
-        <v>46235.51706018519</v>
+        <v>46260.02493055556</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>debceab5-0f85-4262-b03d-642eeb1f7cce</t>
+          <t>263303ce-a0d2-41a7-9a97-0b8ffa3dd331</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>b0f3a909-ced0-49cd-b8b4-434502df5de6</t>
+          <t>f46b2462-0c66-4d81-a4ff-b279f7b44796</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -7961,18 +7961,18 @@
         </is>
       </c>
       <c r="F251" s="2" t="n">
-        <v>46235.51581018518</v>
+        <v>46260.02368055555</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>55d0295a-689b-41a4-9988-0ca4c007368b</t>
+          <t>a33b5a26-ddc8-4ff1-a54d-a30499b46594</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>9ec9f95e-1468-4c4f-a006-fca793e34aa1</t>
+          <t>34595e62-cdb5-4611-ae38-ae6724226212</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -7991,28 +7991,28 @@
         </is>
       </c>
       <c r="F252" s="2" t="n">
-        <v>46235.51688657407</v>
+        <v>46260.02475694445</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>b30a4388-6945-4cca-8ba0-939f2aabd2c0</t>
+          <t>b53c3647-87de-454a-9d10-b3a9f727fda0</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>232a8a87-2155-40f0-bd81-263575258afe</t>
+          <t>edad974c-47fc-4693-b9ec-e9da03b5ea56</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -8021,18 +8021,18 @@
         </is>
       </c>
       <c r="F253" s="2" t="n">
-        <v>46235.51701388889</v>
+        <v>46260.02488425926</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>6a31571f-7c8e-4fa6-9067-f592328d3712</t>
+          <t>7f8664e2-caac-443e-b7a7-8f79a9e55a5f</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>dffd8ecf-ca39-4aa8-b63f-5e476be76235</t>
+          <t>6dd5280e-5591-455c-a1d4-7cc15b8424b6</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -8051,28 +8051,28 @@
         </is>
       </c>
       <c r="F254" s="2" t="n">
-        <v>46235.51730324074</v>
+        <v>46260.02517361111</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>45b37e7f-2c55-4026-9773-a9b1d12761a6</t>
+          <t>7e33dd08-f3e5-4f6b-8afa-3913a6a4d74b</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>12d56881-85bc-4be4-9a05-a4dc39b3310d</t>
+          <t>87eefbeb-8468-47a5-a5ef-8076259e3d8c</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -8081,28 +8081,28 @@
         </is>
       </c>
       <c r="F255" s="2" t="n">
-        <v>46235.51659722222</v>
+        <v>46260.02446759259</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1ef2f0db-393d-4d85-888b-f5b45b33cff8</t>
+          <t>835287fa-7c8e-4f2f-b988-20ad6d3ceaf8</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>c6842666-a65a-4f9c-acd6-ea0c94e8b0e4</t>
+          <t>8099b68e-df70-43a0-9bef-46a025e6a269</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -8111,28 +8111,28 @@
         </is>
       </c>
       <c r="F256" s="2" t="n">
-        <v>46235.51704861111</v>
+        <v>46260.02491898148</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>61cc5340-fba7-4979-b8dd-7ebd5434b6b0</t>
+          <t>be07fd3e-efb7-4f39-9f85-253070821fe0</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>7ef9145d-263a-4a30-8fcc-bf33769fcada</t>
+          <t>9b6189d8-3a85-49b3-8f68-b7dbdc478b6c</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -8141,18 +8141,18 @@
         </is>
       </c>
       <c r="F257" s="2" t="n">
-        <v>46235.51739583333</v>
+        <v>46260.0252662037</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>358d4ff6-7192-4674-bbb2-5dd0be54c260</t>
+          <t>e98869b1-024b-449b-a189-0a30bfd90b62</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>68da5cfc-5a5c-4f30-adec-3b2cf0ad3570</t>
+          <t>903a9432-6229-4479-b6db-87ba9c19bc68</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -8171,28 +8171,28 @@
         </is>
       </c>
       <c r="F258" s="2" t="n">
-        <v>46235.51599537037</v>
+        <v>46260.02386574074</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>577a734a-ab93-48fb-a69b-a7aa3fa66da5</t>
+          <t>36ecd58e-bf93-4385-82ef-029bc6be9890</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>a9555105-c0be-43b2-9c1e-7f22365601b5</t>
+          <t>ef09fabf-1965-4190-ba4b-a57e30ba4d8e</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -8201,18 +8201,18 @@
         </is>
       </c>
       <c r="F259" s="2" t="n">
-        <v>46235.51679398148</v>
+        <v>46260.02466435185</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>6b1059f9-a51a-4e56-b6a2-a9ade142509f</t>
+          <t>af898048-02ca-4102-ae8e-fb70510d2d58</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>b2762850-de9a-49c0-acfe-e3dd98758868</t>
+          <t>42bbf194-0cb7-44aa-bbae-09280e0d27c8</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -8231,28 +8231,28 @@
         </is>
       </c>
       <c r="F260" s="2" t="n">
-        <v>46235.51719907407</v>
+        <v>46260.02506944445</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>edfda700-b940-410e-86cd-57bf27849b1c</t>
+          <t>747c8af9-5c1c-4af3-88f9-685826e21351</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>ca0e932a-fd81-474f-98cc-1fbc739211f1</t>
+          <t>6f586dd0-d848-4db7-8431-723fe6e5dd48</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -8261,23 +8261,23 @@
         </is>
       </c>
       <c r="F261" s="2" t="n">
-        <v>46235.51579861111</v>
+        <v>46260.02366898148</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>f539d19e-26a5-4151-9b11-2c897092a67d</t>
+          <t>ced9f5a8-34b9-43c8-8308-862e9f9aa262</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>93ee78f6-3f20-4ec8-a586-1b3f409fcb9b</t>
+          <t>c8e35c42-6053-4113-a599-7cc79283d867</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -8291,28 +8291,28 @@
         </is>
       </c>
       <c r="F262" s="2" t="n">
-        <v>46235.51615740741</v>
+        <v>46260.02402777778</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>9aa38739-16c6-44fe-bac2-48908da4c814</t>
+          <t>577cd175-76d9-44b8-a1b8-7005bec5efdf</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>4eb33a36-2364-42a1-8681-0f9ba8b082e5</t>
+          <t>4827461c-8604-4218-935b-97de9b45debf</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -8321,23 +8321,23 @@
         </is>
       </c>
       <c r="F263" s="2" t="n">
-        <v>46235.51584490741</v>
+        <v>46260.02371527778</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>4d032d45-e74d-49d1-92d6-888b9f45be33</t>
+          <t>14771eba-4c61-4651-95b1-c70979bb48b1</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>517f640d-86a9-424b-a565-c57460d72399</t>
+          <t>6469a201-c598-4bc6-b451-765e0d37845d</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -8351,28 +8351,28 @@
         </is>
       </c>
       <c r="F264" s="2" t="n">
-        <v>46235.51737268519</v>
+        <v>46260.02524305556</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>89104845-1f4e-4121-9f4e-6dd78694c6dc</t>
+          <t>2285a7f0-b25c-43bc-b0e5-4082b1d29b0a</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>7853563e-dd48-4b33-bee8-b176567a1ff7</t>
+          <t>178dc3a5-ac00-4268-8cd4-9d9bab93c92a</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -8381,28 +8381,28 @@
         </is>
       </c>
       <c r="F265" s="2" t="n">
-        <v>46235.51666666667</v>
+        <v>46260.02453703704</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>375e8b33-e20a-4fe2-823e-5ae621e5c10c</t>
+          <t>4f166fea-6985-43c1-8412-bd94da2e88a3</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>c32a0539-b376-4ee2-8e59-8cb2768efd15</t>
+          <t>74532582-b900-4d1d-ad1a-54d3e0b2f77e</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -8411,23 +8411,23 @@
         </is>
       </c>
       <c r="F266" s="2" t="n">
-        <v>46235.51701388889</v>
+        <v>46260.02488425926</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>e0cddab8-c1bc-4e15-b2d2-4098abd2a552</t>
+          <t>e9f69e3e-fb2a-402c-bcc8-72e590c58a8f</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>f0b2aa71-8809-4d4a-a04f-dfcb3b546765</t>
+          <t>42c21d36-88f7-4dd6-be02-20b2eb90c142</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -8441,18 +8441,18 @@
         </is>
       </c>
       <c r="F267" s="2" t="n">
-        <v>46235.51627314815</v>
+        <v>46260.02414351852</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>b62a22e5-cec9-4611-875d-2cff7639c924</t>
+          <t>b5494cad-fac7-4372-a63b-8daea868be2c</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>b761ef69-3aa4-4d36-830c-04148f5d05a6</t>
+          <t>92f65ded-d3ad-4f3d-8ef4-ac62c5fe252b</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -8471,28 +8471,28 @@
         </is>
       </c>
       <c r="F268" s="2" t="n">
-        <v>46235.51741898148</v>
+        <v>46260.02528935186</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>569f806d-a344-4647-a388-00379bb86cc1</t>
+          <t>1c0084e0-2f90-4d67-b3e3-a2a8e2a61165</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>68da5cfc-5a5c-4f30-adec-3b2cf0ad3570</t>
+          <t>67e56e91-8a9d-404b-b870-8db751571e05</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -8501,18 +8501,18 @@
         </is>
       </c>
       <c r="F269" s="2" t="n">
-        <v>46235.51597222222</v>
+        <v>46260.02384259259</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>24b08867-5b04-45be-aec1-e7e6d59574d9</t>
+          <t>88889971-d9fa-4c9e-8ce8-82ec88f24f64</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>7622805e-1891-43b3-9d99-dfe5f0b1ab76</t>
+          <t>2febe67b-0ff0-4a57-8df5-6dff3dceebfa</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -8531,23 +8531,23 @@
         </is>
       </c>
       <c r="F270" s="2" t="n">
-        <v>46235.51770833333</v>
+        <v>46260.0255787037</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>e564f1e5-a86a-4003-a504-9623403ae9b1</t>
+          <t>1ea0be06-9197-43cb-81a6-dfd4ed72bd76</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>c6842666-a65a-4f9c-acd6-ea0c94e8b0e4</t>
+          <t>03ef7674-d310-4656-89de-08e3f167e1ba</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -8561,28 +8561,28 @@
         </is>
       </c>
       <c r="F271" s="2" t="n">
-        <v>46235.51646990741</v>
+        <v>46260.02434027778</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>847e4ea0-e5cc-432b-96f6-36ee872e291a</t>
+          <t>18ddd87c-3bb4-49a7-ab25-7fcb9c7868a3</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>831d7f10-2c81-480d-bdae-c7135346307a</t>
+          <t>03959483-600c-4879-942b-25902022410d</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -8591,18 +8591,18 @@
         </is>
       </c>
       <c r="F272" s="2" t="n">
-        <v>46235.51664351852</v>
+        <v>46260.02451388889</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>c0ba411d-c8dc-4f18-bf86-6d40849ede4e</t>
+          <t>598ed86a-a833-4ad9-987e-33555e0241de</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>217d8d97-267f-42b8-b0c4-0e9892150141</t>
+          <t>9abe646f-9247-4c8f-8c1d-509abe328744</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -8621,18 +8621,18 @@
         </is>
       </c>
       <c r="F273" s="2" t="n">
-        <v>46235.51607638889</v>
+        <v>46260.02394675926</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>6f4fa112-80b2-465f-8dbe-78f57ca00267</t>
+          <t>0c340f38-9d6c-49be-8a3e-4fbfe874e0cb</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>ba260fd8-7e47-43f3-8e00-c47c3bc12abe</t>
+          <t>9274faa9-fd95-4d89-ba77-8b3b66d3ae52</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -8651,18 +8651,18 @@
         </is>
       </c>
       <c r="F274" s="2" t="n">
-        <v>46235.51695601852</v>
+        <v>46260.02482638889</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>21f0714e-431c-46f8-b49f-f84d4714de9d</t>
+          <t>d17e85e7-135e-4a39-88f3-2f20572f2fbf</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>d3d0a42e-ef8b-4011-b9b7-ccd514c1089e</t>
+          <t>ce6c30f4-ac3a-4b5c-81d0-f7f9c1d356d6</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -8681,28 +8681,28 @@
         </is>
       </c>
       <c r="F275" s="2" t="n">
-        <v>46235.51756944445</v>
+        <v>46260.02543981482</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>d4106095-f36c-4a7a-ba21-912bd092c5ac</t>
+          <t>12a5e636-6373-4bfc-b54c-38b71da3f27f</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>528e0b43-675f-4a03-bf5f-78a08c2a4203</t>
+          <t>15b29fb8-7d6d-4b8d-913e-9a965faef996</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -8711,23 +8711,23 @@
         </is>
       </c>
       <c r="F276" s="2" t="n">
-        <v>46235.51611111111</v>
+        <v>46260.02398148148</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>b2d93175-a64a-4195-9c20-ad7a188c1bc7</t>
+          <t>e200cb8f-357a-4f59-ac62-42bebcf963d0</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>c8ba352f-ba91-4913-975f-71f16968349b</t>
+          <t>ac1c07c9-3e8b-46e4-a18f-755c6bcf1400</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -8741,18 +8741,18 @@
         </is>
       </c>
       <c r="F277" s="2" t="n">
-        <v>46235.51631944445</v>
+        <v>46260.02418981482</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>17b3be31-ffeb-46ae-8ca9-faa0649ff18e</t>
+          <t>4c6ed8a3-5603-46d2-89f0-c3dfc101b718</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>e210878d-9aeb-48b8-b43e-0950146d4e39</t>
+          <t>6f586dd0-d848-4db7-8431-723fe6e5dd48</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -8771,28 +8771,28 @@
         </is>
       </c>
       <c r="F278" s="2" t="n">
-        <v>46235.51715277778</v>
+        <v>46260.02502314815</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>bf9916e9-21ed-4a1d-bce1-03a5d14d822b</t>
+          <t>ec3718dd-bcd2-4892-979d-a4a177e04597</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>69b84e67-3b6f-43f6-be94-61afd6b646f9</t>
+          <t>328cd713-fb14-4086-99b8-57a7055eff30</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -8801,28 +8801,28 @@
         </is>
       </c>
       <c r="F279" s="2" t="n">
-        <v>46235.51675925926</v>
+        <v>46260.02462962963</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>b97489d7-b06e-40b3-ae79-fa372ee91385</t>
+          <t>6f7da39b-b4a2-439c-aded-850bd85882eb</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>cf1b0121-6f25-47c3-9604-0e6f193fe8f0</t>
+          <t>80001165-bfd4-436f-a450-21d6ea84544d</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -8831,18 +8831,18 @@
         </is>
       </c>
       <c r="F280" s="2" t="n">
-        <v>46235.51675925926</v>
+        <v>46260.02462962963</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>d4bdb2ec-a47d-489c-afc2-4267fd4e9604</t>
+          <t>c765856b-bcde-456f-9853-bd740c1be59f</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>8892a89b-9ad4-4f12-9eea-7486c41091bc</t>
+          <t>74532582-b900-4d1d-ad1a-54d3e0b2f77e</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -8861,28 +8861,28 @@
         </is>
       </c>
       <c r="F281" s="2" t="n">
-        <v>46235.51778935185</v>
+        <v>46260.02565972223</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>22fd778c-0b32-47ea-99d9-f3d936ff1493</t>
+          <t>051b2c73-bedb-4802-9f0c-d88afee02c21</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>55423194-fdc8-4f32-839d-77611bcdfc4b</t>
+          <t>b4417c0f-3d7e-4f01-b12c-b52af4b2ece7</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -8891,18 +8891,18 @@
         </is>
       </c>
       <c r="F282" s="2" t="n">
-        <v>46235.51607638889</v>
+        <v>46260.02394675926</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>c9d79f3e-8e02-4a35-aead-064c67eabed5</t>
+          <t>485596ae-2834-41a0-97d6-46c9185a6356</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2e9ef7de-9919-42d3-bda6-3521e6b0363c</t>
+          <t>2febe67b-0ff0-4a57-8df5-6dff3dceebfa</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -8921,18 +8921,18 @@
         </is>
       </c>
       <c r="F283" s="2" t="n">
-        <v>46235.51770833333</v>
+        <v>46260.0255787037</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2d1cb944-bdfb-41d8-b858-88c3d68ceabb</t>
+          <t>efd7d6cd-d9ea-45fb-8f07-9b49bb806ab5</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>dddd2e85-b285-4b10-9d71-da03c4dfdbcf</t>
+          <t>f0728245-7667-48c1-9d95-e88292e07edc</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -8951,23 +8951,23 @@
         </is>
       </c>
       <c r="F284" s="2" t="n">
-        <v>46235.51696759259</v>
+        <v>46260.02483796296</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>ee609dca-0cd3-4d53-a697-12d132de4868</t>
+          <t>8e2a3f2a-a2c2-4b6e-a535-cda5088c8f05</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>b4bcd554-429d-4560-9171-eecf27d4d4b4</t>
+          <t>f2029fb7-2b7a-4d0f-8151-0bb51d7d1a1e</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -8981,28 +8981,28 @@
         </is>
       </c>
       <c r="F285" s="2" t="n">
-        <v>46235.51716435186</v>
+        <v>46260.02503472222</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>154f7074-1c63-46fb-9174-1ec531da831d</t>
+          <t>9256808e-3c16-4529-8506-35ef03dd6e6e</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2286ba20-88d5-4e98-b15a-a4a2f55da2e5</t>
+          <t>e77d4500-ab6b-444e-bd4a-ce9e608a4669</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -9011,18 +9011,18 @@
         </is>
       </c>
       <c r="F286" s="2" t="n">
-        <v>46235.51577546296</v>
+        <v>46260.02364583333</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>28aecb01-66e8-4d1e-8915-211a0d7d2439</t>
+          <t>3054f913-6d3f-47ef-9671-e75acd5e13a4</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>528e0b43-675f-4a03-bf5f-78a08c2a4203</t>
+          <t>483718f8-e416-41cd-904d-7a237019c393</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -9041,18 +9041,18 @@
         </is>
       </c>
       <c r="F287" s="2" t="n">
-        <v>46235.51711805556</v>
+        <v>46260.02498842592</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>522754eb-c77b-4aa4-ba9f-8a195c28bdd0</t>
+          <t>381f4abe-c8a4-4800-8a5b-7a3780931de7</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>072fd290-6796-4c10-b607-70db53cdb727</t>
+          <t>d8832129-bed7-41dd-8635-4db7bdc3afb1</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -9071,28 +9071,28 @@
         </is>
       </c>
       <c r="F288" s="2" t="n">
-        <v>46235.51591435185</v>
+        <v>46260.02378472222</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>ddcbf80b-d6b9-4151-ac01-9ef46955c6b5</t>
+          <t>172e541c-bddb-4e30-9c1e-fa8c9ede87f0</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>43d568c5-52bc-4c5d-b7e6-9c703846aaf6</t>
+          <t>48781524-dc37-4660-adff-9d43533ef266</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -9101,18 +9101,18 @@
         </is>
       </c>
       <c r="F289" s="2" t="n">
-        <v>46235.51659722222</v>
+        <v>46260.02446759259</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>9b943cbd-9e05-4807-a29c-95bff69f2571</t>
+          <t>5f8f6276-b044-47bf-8d50-649114d0195b</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>b4bcd554-429d-4560-9171-eecf27d4d4b4</t>
+          <t>0566f9df-30ab-44ee-81c2-56f47a689fbc</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -9131,28 +9131,28 @@
         </is>
       </c>
       <c r="F290" s="2" t="n">
-        <v>46235.51696759259</v>
+        <v>46260.02483796296</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>a9a1e02d-e8fd-497a-af11-26959a7fe001</t>
+          <t>884ab40b-4342-403d-abab-0a5df7d115e9</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>edf33408-32f0-4023-8f23-d2976b8c6f24</t>
+          <t>1be043c1-4206-49fb-9377-b4a0ed2b32a9</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Campaign_Blast</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -9161,28 +9161,28 @@
         </is>
       </c>
       <c r="F291" s="2" t="n">
-        <v>46235.51759259259</v>
+        <v>46260.02546296296</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>ba2ff7bb-bdcc-44da-8f25-cbfeaa4c03d6</t>
+          <t>b1f95f92-f078-489f-b687-65c56de9a209</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>4b177a79-1e3b-4908-a573-43c662c3a15b</t>
+          <t>f53d985f-2219-497c-93c4-97f25f762f7d</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -9191,18 +9191,18 @@
         </is>
       </c>
       <c r="F292" s="2" t="n">
-        <v>46235.51730324074</v>
+        <v>46260.02517361111</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>60855689-0a45-4aa1-879a-8ccc7299f14c</t>
+          <t>f3dc9ece-3e89-4ecf-81f2-688cde5af1bb</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>f400192e-4d6f-4f9f-8b33-bcf900ded667</t>
+          <t>972f3eca-17b8-4a72-bcf2-34168a923e4d</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -9221,23 +9221,23 @@
         </is>
       </c>
       <c r="F293" s="2" t="n">
-        <v>46235.51586805555</v>
+        <v>46260.02373842592</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>c8ca304a-9e47-42bd-8e8a-42cbd1d9bff3</t>
+          <t>e56e0035-7b4f-4ba3-9802-fe6309992e5a</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>cf1b0121-6f25-47c3-9604-0e6f193fe8f0</t>
+          <t>0d43b730-1055-43fb-a8e0-51a89c415253</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -9251,18 +9251,18 @@
         </is>
       </c>
       <c r="F294" s="2" t="n">
-        <v>46235.51767361111</v>
+        <v>46260.02554398148</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>1ce45897-eebb-4dfc-ad9d-c9474e028957</t>
+          <t>8b649529-5421-4737-902a-e09a014d7391</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>b38830eb-c104-4bc5-91e8-9bc1235d80f0</t>
+          <t>a8f0020c-6daa-4fe6-8f45-df1383ad979a</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -9281,28 +9281,28 @@
         </is>
       </c>
       <c r="F295" s="2" t="n">
-        <v>46235.51635416667</v>
+        <v>46260.02422453704</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2ee0112a-bc05-4793-a4ab-f87d782881be</t>
+          <t>ee91e15d-6b1d-4653-af9f-31e87ff2f22c</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>55423194-fdc8-4f32-839d-77611bcdfc4b</t>
+          <t>eb4dfbe2-142c-41d0-97d1-eb96e9c5681f</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>AI_Chat</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -9311,28 +9311,28 @@
         </is>
       </c>
       <c r="F296" s="2" t="n">
-        <v>46235.51667824074</v>
+        <v>46260.02454861111</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>0d2e29a7-ab9b-44f0-85dd-4b6418a0ff10</t>
+          <t>abff103f-577f-4a99-b3dc-e46e3495f22d</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>8ec5a72f-306a-4db1-9c6e-8bb0901c4600</t>
+          <t>34595e62-cdb5-4611-ae38-ae6724226212</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Payment_Reminder</t>
+          <t>Campaign_Blast</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -9341,18 +9341,18 @@
         </is>
       </c>
       <c r="F297" s="2" t="n">
-        <v>46235.51677083333</v>
+        <v>46260.0246412037</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>e19ecbe1-6bc4-443d-b2ad-31ac3a2e37d6</t>
+          <t>5021d253-e38f-46e5-a444-d1e70c6cc175</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>35deb745-979c-4203-a34a-6b1a73683f7e</t>
+          <t>7759edef-05d4-45b5-8d73-26ff21a8f5f0</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -9371,28 +9371,28 @@
         </is>
       </c>
       <c r="F298" s="2" t="n">
-        <v>46235.51733796296</v>
+        <v>46260.02520833333</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>780246c2-ee09-48fe-954a-c18f58a48b55</t>
+          <t>a2aa958d-39ed-466a-a952-6fdd2ee0bfb3</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>c54622a9-766f-4b0a-9ca6-107e30205d18</t>
+          <t>87eefbeb-8468-47a5-a5ef-8076259e3d8c</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -9401,18 +9401,18 @@
         </is>
       </c>
       <c r="F299" s="2" t="n">
-        <v>46235.51631944445</v>
+        <v>46260.02418981482</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>6579c58f-07f9-422a-89f2-c96978e34be0</t>
+          <t>5e0ae6c6-64e5-4eef-887a-9933d9a6f0e7</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>f5682ea1-5450-43ea-84c9-4daeb84ee1f9</t>
+          <t>931f45dc-af13-4c07-b037-a965806d604b</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Quote_Sent</t>
+          <t>Payment_Reminder</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -9431,18 +9431,18 @@
         </is>
       </c>
       <c r="F300" s="2" t="n">
-        <v>46235.51605324074</v>
+        <v>46260.02392361111</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>c39cf063-c7c7-469f-acf5-fa513efb6aae</t>
+          <t>c3a9ec99-4603-4acd-8a12-52eb0a131066</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>6a63e8be-946a-48d1-bba1-d2b767bbc3e4</t>
+          <t>a8f0020c-6daa-4fe6-8f45-df1383ad979a</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>AI_Chat</t>
+          <t>Quote_Sent</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -9461,7 +9461,7 @@
         </is>
       </c>
       <c r="F301" s="2" t="n">
-        <v>46235.51758101852</v>
+        <v>46260.02545138889</v>
       </c>
     </row>
   </sheetData>
